--- a/research/traditional_assets/database/data/czech_republic/czech_republic_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_aerospace_defense.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09149768068724076</v>
+        <v>0.09136028509393501</v>
       </c>
       <c r="C2">
-        <v>2317.285463507145</v>
+        <v>2299.016509787588</v>
       </c>
       <c r="D2">
-        <v>2083.785463507145</v>
+        <v>2090.069509787588</v>
       </c>
       <c r="E2">
-        <v>-903.3</v>
+        <v>-878.747</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24.553</v>
       </c>
       <c r="G2">
         <v>233.5</v>
@@ -1576,28 +1576,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.2350159</v>
       </c>
       <c r="N2">
-        <v>132.2666666666667</v>
+        <v>131.0316507666666</v>
       </c>
       <c r="O2">
-        <v>25.13066666666666</v>
+        <v>24.89601364566666</v>
       </c>
       <c r="P2">
-        <v>107.136</v>
+        <v>106.135637121</v>
       </c>
       <c r="Q2">
-        <v>161.136</v>
+        <v>160.135637121</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09149768068724076</v>
+        <v>0.09187157080195456</v>
       </c>
       <c r="T2">
-        <v>0.8907328536426569</v>
+        <v>0.8980206678997332</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>107.0971366981321</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09136028509393501</v>
+        <v>0.09122288950062926</v>
       </c>
       <c r="C3">
-        <v>2299.016509787588</v>
+        <v>2280.785572155362</v>
       </c>
       <c r="D3">
-        <v>2090.069509787588</v>
+        <v>2096.391572155363</v>
       </c>
       <c r="E3">
-        <v>-878.747</v>
+        <v>-854.194</v>
       </c>
       <c r="F3">
-        <v>24.553</v>
+        <v>49.106</v>
       </c>
       <c r="G3">
         <v>233.5</v>
@@ -1658,28 +1658,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M3">
-        <v>1.2350159</v>
+        <v>2.4700318</v>
       </c>
       <c r="N3">
-        <v>131.0316507666666</v>
+        <v>129.7966348666667</v>
       </c>
       <c r="O3">
-        <v>24.89601364566666</v>
+        <v>24.66136062466667</v>
       </c>
       <c r="P3">
-        <v>106.135637121</v>
+        <v>105.135274242</v>
       </c>
       <c r="Q3">
-        <v>160.135637121</v>
+        <v>159.135274242</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09187157080195456</v>
+        <v>0.09225309132717271</v>
       </c>
       <c r="T3">
-        <v>0.8980206678997332</v>
+        <v>0.9054572130600151</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>107.0971366981321</v>
+        <v>53.54856834906606</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09122288950062926</v>
+        <v>0.0910854939073235</v>
       </c>
       <c r="C4">
-        <v>2280.785572155362</v>
+        <v>2262.592996631398</v>
       </c>
       <c r="D4">
-        <v>2096.391572155363</v>
+        <v>2102.751996631398</v>
       </c>
       <c r="E4">
-        <v>-854.194</v>
+        <v>-829.641</v>
       </c>
       <c r="F4">
-        <v>49.106</v>
+        <v>73.65900000000001</v>
       </c>
       <c r="G4">
         <v>233.5</v>
@@ -1740,28 +1740,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M4">
-        <v>2.4700318</v>
+        <v>3.7050477</v>
       </c>
       <c r="N4">
-        <v>129.7966348666667</v>
+        <v>128.5616189666667</v>
       </c>
       <c r="O4">
-        <v>24.66136062466667</v>
+        <v>24.42670760366666</v>
       </c>
       <c r="P4">
-        <v>105.135274242</v>
+        <v>104.134911363</v>
       </c>
       <c r="Q4">
-        <v>159.135274242</v>
+        <v>158.134911363</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09225309132717271</v>
+        <v>0.09264247825497268</v>
       </c>
       <c r="T4">
-        <v>0.9054572130600151</v>
+        <v>0.9130470890483441</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>53.54856834906606</v>
+        <v>35.69904556604403</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0910854939073235</v>
+        <v>0.09094809831401773</v>
       </c>
       <c r="C5">
-        <v>2262.592996631398</v>
+        <v>2244.439133448692</v>
       </c>
       <c r="D5">
-        <v>2102.751996631398</v>
+        <v>2109.151133448692</v>
       </c>
       <c r="E5">
-        <v>-829.641</v>
+        <v>-805.088</v>
       </c>
       <c r="F5">
-        <v>73.65900000000001</v>
+        <v>98.212</v>
       </c>
       <c r="G5">
         <v>233.5</v>
@@ -1822,28 +1822,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M5">
-        <v>3.7050477</v>
+        <v>4.9400636</v>
       </c>
       <c r="N5">
-        <v>128.5616189666667</v>
+        <v>127.3266030666666</v>
       </c>
       <c r="O5">
-        <v>24.42670760366666</v>
+        <v>24.19205458266666</v>
       </c>
       <c r="P5">
-        <v>104.134911363</v>
+        <v>103.134548484</v>
       </c>
       <c r="Q5">
-        <v>158.134911363</v>
+        <v>157.134548484</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09264247825497268</v>
+        <v>0.09303997741043514</v>
       </c>
       <c r="T5">
-        <v>0.9130470890483441</v>
+        <v>0.9207950874530965</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>35.69904556604403</v>
+        <v>26.77428417453303</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09094809831401773</v>
+        <v>0.09081070272071197</v>
       </c>
       <c r="C6">
-        <v>2244.439133448692</v>
+        <v>2226.324337116603</v>
       </c>
       <c r="D6">
-        <v>2109.151133448692</v>
+        <v>2115.589337116603</v>
       </c>
       <c r="E6">
-        <v>-805.088</v>
+        <v>-780.535</v>
       </c>
       <c r="F6">
-        <v>98.212</v>
+        <v>122.765</v>
       </c>
       <c r="G6">
         <v>233.5</v>
@@ -1904,28 +1904,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M6">
-        <v>4.9400636</v>
+        <v>6.175079500000001</v>
       </c>
       <c r="N6">
-        <v>127.3266030666666</v>
+        <v>126.0915871666667</v>
       </c>
       <c r="O6">
-        <v>24.19205458266666</v>
+        <v>23.95740156166666</v>
       </c>
       <c r="P6">
-        <v>103.134548484</v>
+        <v>102.134185605</v>
       </c>
       <c r="Q6">
-        <v>157.134548484</v>
+        <v>156.134185605</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09303997741043514</v>
+        <v>0.09344584496917049</v>
       </c>
       <c r="T6">
-        <v>0.9207950874530965</v>
+        <v>0.9287062016137385</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.77428417453303</v>
+        <v>21.41942733962642</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09081070272071197</v>
+        <v>0.09067330712740622</v>
       </c>
       <c r="C7">
-        <v>2226.324337116603</v>
+        <v>2208.248966486311</v>
       </c>
       <c r="D7">
-        <v>2115.589337116603</v>
+        <v>2122.066966486312</v>
       </c>
       <c r="E7">
-        <v>-780.535</v>
+        <v>-755.982</v>
       </c>
       <c r="F7">
-        <v>122.765</v>
+        <v>147.318</v>
       </c>
       <c r="G7">
         <v>233.5</v>
@@ -1986,28 +1986,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M7">
-        <v>6.175079500000001</v>
+        <v>7.4100954</v>
       </c>
       <c r="N7">
-        <v>126.0915871666667</v>
+        <v>124.8565712666666</v>
       </c>
       <c r="O7">
-        <v>23.95740156166666</v>
+        <v>23.72274854066666</v>
       </c>
       <c r="P7">
-        <v>102.134185605</v>
+        <v>101.133822726</v>
       </c>
       <c r="Q7">
-        <v>156.134185605</v>
+        <v>155.133822726</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09344584496917049</v>
+        <v>0.09386034800787896</v>
       </c>
       <c r="T7">
-        <v>0.9287062016137385</v>
+        <v>0.9367856373522665</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.41942733962642</v>
+        <v>17.84952278302202</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09067330712740622</v>
+        <v>0.09053591153410048</v>
       </c>
       <c r="C8">
-        <v>2208.248966486311</v>
+        <v>2190.213384817503</v>
       </c>
       <c r="D8">
-        <v>2122.066966486312</v>
+        <v>2128.584384817503</v>
       </c>
       <c r="E8">
-        <v>-755.982</v>
+        <v>-731.429</v>
       </c>
       <c r="F8">
-        <v>147.318</v>
+        <v>171.871</v>
       </c>
       <c r="G8">
         <v>233.5</v>
@@ -2068,28 +2068,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M8">
-        <v>7.4100954</v>
+        <v>8.645111299999998</v>
       </c>
       <c r="N8">
-        <v>124.8565712666666</v>
+        <v>123.6215553666667</v>
       </c>
       <c r="O8">
-        <v>23.72274854066666</v>
+        <v>23.48809551966666</v>
       </c>
       <c r="P8">
-        <v>101.133822726</v>
+        <v>100.133459847</v>
       </c>
       <c r="Q8">
-        <v>155.133822726</v>
+        <v>154.133459847</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09386034800787896</v>
+        <v>0.09428376509043061</v>
       </c>
       <c r="T8">
-        <v>0.9367856373522665</v>
+        <v>0.9450388243969996</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.84952278302202</v>
+        <v>15.29959095687602</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09053591153410047</v>
+        <v>0.09039851594079472</v>
       </c>
       <c r="C9">
-        <v>2190.213384817503</v>
+        <v>2172.217959846269</v>
       </c>
       <c r="D9">
-        <v>2128.584384817503</v>
+        <v>2135.141959846269</v>
       </c>
       <c r="E9">
-        <v>-731.4289999999999</v>
+        <v>-706.876</v>
       </c>
       <c r="F9">
-        <v>171.871</v>
+        <v>196.424</v>
       </c>
       <c r="G9">
         <v>233.5</v>
@@ -2150,28 +2150,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M9">
-        <v>8.645111300000002</v>
+        <v>9.8801272</v>
       </c>
       <c r="N9">
-        <v>123.6215553666667</v>
+        <v>122.3865394666666</v>
       </c>
       <c r="O9">
-        <v>23.48809551966666</v>
+        <v>23.25344249866667</v>
       </c>
       <c r="P9">
-        <v>100.133459847</v>
+        <v>99.13309696799999</v>
       </c>
       <c r="Q9">
-        <v>154.133459847</v>
+        <v>153.133096968</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09428376509043061</v>
+        <v>0.09471638689216816</v>
       </c>
       <c r="T9">
-        <v>0.9450388243969996</v>
+        <v>0.9534714285514005</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.29959095687601</v>
+        <v>13.38714208726651</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09039851594079472</v>
+        <v>0.09037047034748895</v>
       </c>
       <c r="C10">
-        <v>2172.217959846269</v>
+        <v>2149.008479952498</v>
       </c>
       <c r="D10">
-        <v>2135.141959846269</v>
+        <v>2136.485479952498</v>
       </c>
       <c r="E10">
-        <v>-706.876</v>
+        <v>-682.323</v>
       </c>
       <c r="F10">
-        <v>196.424</v>
+        <v>220.977</v>
       </c>
       <c r="G10">
         <v>233.5</v>
@@ -2232,45 +2232,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M10">
-        <v>9.8801272</v>
+        <v>11.4466086</v>
       </c>
       <c r="N10">
-        <v>122.3865394666666</v>
+        <v>120.8200580666666</v>
       </c>
       <c r="O10">
-        <v>23.25344249866667</v>
+        <v>22.95581103266666</v>
       </c>
       <c r="P10">
-        <v>99.13309696799999</v>
+        <v>97.86424703399999</v>
       </c>
       <c r="Q10">
-        <v>153.133096968</v>
+        <v>151.864247034</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09471638689216816</v>
+        <v>0.09515851686537247</v>
       </c>
       <c r="T10">
-        <v>0.9534714285514005</v>
+        <v>0.9620893646652389</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.19</v>
       </c>
       <c r="W10">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.38714208726651</v>
+        <v>11.55509647343639</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09037047034748895</v>
+        <v>0.0902452247541832</v>
       </c>
       <c r="C11">
-        <v>2149.008479952498</v>
+        <v>2130.476045558943</v>
       </c>
       <c r="D11">
-        <v>2136.485479952498</v>
+        <v>2142.506045558943</v>
       </c>
       <c r="E11">
-        <v>-682.323</v>
+        <v>-657.77</v>
       </c>
       <c r="F11">
-        <v>220.977</v>
+        <v>245.53</v>
       </c>
       <c r="G11">
         <v>233.5</v>
@@ -2314,28 +2314,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M11">
-        <v>11.4466086</v>
+        <v>12.718454</v>
       </c>
       <c r="N11">
-        <v>120.8200580666666</v>
+        <v>119.5482126666667</v>
       </c>
       <c r="O11">
-        <v>22.95581103266666</v>
+        <v>22.71416040666666</v>
       </c>
       <c r="P11">
-        <v>97.86424703399999</v>
+        <v>96.83405225999999</v>
       </c>
       <c r="Q11">
-        <v>151.864247034</v>
+        <v>150.83405226</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09515851686537247</v>
+        <v>0.09561047194909245</v>
       </c>
       <c r="T11">
-        <v>0.9620893646652389</v>
+        <v>0.9708988104704961</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.55509647343639</v>
+        <v>10.39958682609275</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0902452247541832</v>
+        <v>0.09027144916087744</v>
       </c>
       <c r="C12">
-        <v>2130.476045558943</v>
+        <v>2104.659629345985</v>
       </c>
       <c r="D12">
-        <v>2142.506045558943</v>
+        <v>2141.242629345985</v>
       </c>
       <c r="E12">
-        <v>-657.77</v>
+        <v>-633.2169999999999</v>
       </c>
       <c r="F12">
-        <v>245.53</v>
+        <v>270.083</v>
       </c>
       <c r="G12">
         <v>233.5</v>
@@ -2396,45 +2396,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M12">
-        <v>12.718454</v>
+        <v>14.4494405</v>
       </c>
       <c r="N12">
-        <v>119.5482126666666</v>
+        <v>117.8172261666666</v>
       </c>
       <c r="O12">
-        <v>22.71416040666666</v>
+        <v>22.38527297166666</v>
       </c>
       <c r="P12">
-        <v>96.83405225999998</v>
+        <v>95.43195319499998</v>
       </c>
       <c r="Q12">
-        <v>150.83405226</v>
+        <v>149.431953195</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09561047194909245</v>
+        <v>0.09607258332682858</v>
       </c>
       <c r="T12">
-        <v>0.9708988104704961</v>
+        <v>0.9799062213500285</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.19</v>
       </c>
       <c r="W12">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.39958682609275</v>
+        <v>9.153756968421485</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09027144916087744</v>
+        <v>0.09015997356757167</v>
       </c>
       <c r="C13">
-        <v>2104.659629345985</v>
+        <v>2085.487522825426</v>
       </c>
       <c r="D13">
-        <v>2141.242629345985</v>
+        <v>2146.623522825426</v>
       </c>
       <c r="E13">
-        <v>-633.2169999999999</v>
+        <v>-608.664</v>
       </c>
       <c r="F13">
-        <v>270.083</v>
+        <v>294.636</v>
       </c>
       <c r="G13">
         <v>233.5</v>
@@ -2478,28 +2478,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M13">
-        <v>14.4494405</v>
+        <v>15.763026</v>
       </c>
       <c r="N13">
-        <v>117.8172261666666</v>
+        <v>116.5036406666667</v>
       </c>
       <c r="O13">
-        <v>22.38527297166666</v>
+        <v>22.13569172666666</v>
       </c>
       <c r="P13">
-        <v>95.43195319499998</v>
+        <v>94.36794893999999</v>
       </c>
       <c r="Q13">
-        <v>149.431953195</v>
+        <v>148.36794894</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09607258332682858</v>
+        <v>0.0965451972358769</v>
       </c>
       <c r="T13">
-        <v>0.9799062213500285</v>
+        <v>0.9891183461131866</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.153756968421485</v>
+        <v>8.390943887719697</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09015997356757167</v>
+        <v>0.09004849797426592</v>
       </c>
       <c r="C14">
-        <v>2085.487522825426</v>
+        <v>2066.342528560451</v>
       </c>
       <c r="D14">
-        <v>2146.623522825426</v>
+        <v>2152.031528560451</v>
       </c>
       <c r="E14">
-        <v>-608.664</v>
+        <v>-584.1109999999999</v>
       </c>
       <c r="F14">
-        <v>294.636</v>
+        <v>319.189</v>
       </c>
       <c r="G14">
         <v>233.5</v>
@@ -2560,28 +2560,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M14">
-        <v>15.763026</v>
+        <v>17.0766115</v>
       </c>
       <c r="N14">
-        <v>116.5036406666667</v>
+        <v>115.1900551666667</v>
       </c>
       <c r="O14">
-        <v>22.13569172666666</v>
+        <v>21.88611048166667</v>
       </c>
       <c r="P14">
-        <v>94.36794893999999</v>
+        <v>93.30394468499999</v>
       </c>
       <c r="Q14">
-        <v>148.36794894</v>
+        <v>147.303944685</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0965451972358769</v>
+        <v>0.09702867583248956</v>
       </c>
       <c r="T14">
-        <v>0.9891183461131866</v>
+        <v>0.998542243859406</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.390943887719697</v>
+        <v>7.745486665587412</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09004849797426592</v>
+        <v>0.09002774238096017</v>
       </c>
       <c r="C15">
-        <v>2066.342528560451</v>
+        <v>2042.799453299615</v>
       </c>
       <c r="D15">
-        <v>2152.031528560451</v>
+        <v>2153.041453299616</v>
       </c>
       <c r="E15">
-        <v>-584.1109999999999</v>
+        <v>-559.5579999999999</v>
       </c>
       <c r="F15">
-        <v>319.189</v>
+        <v>343.7420000000001</v>
       </c>
       <c r="G15">
         <v>233.5</v>
@@ -2642,45 +2642,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M15">
-        <v>17.0766115</v>
+        <v>18.66519060000001</v>
       </c>
       <c r="N15">
-        <v>115.1900551666667</v>
+        <v>113.6014760666666</v>
       </c>
       <c r="O15">
-        <v>21.88611048166667</v>
+        <v>21.58428045266666</v>
       </c>
       <c r="P15">
-        <v>93.30394468499999</v>
+        <v>92.01719561399999</v>
       </c>
       <c r="Q15">
-        <v>147.303944685</v>
+        <v>146.017195614</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09702867583248956</v>
+        <v>0.09752339811739555</v>
       </c>
       <c r="T15">
-        <v>0.998542243859406</v>
+        <v>1.008185302018328</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.19</v>
       </c>
       <c r="W15">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.745486665587412</v>
+        <v>7.086274632880878</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09002774238096017</v>
+        <v>0.08992274678765441</v>
       </c>
       <c r="C16">
-        <v>2042.799453299615</v>
+        <v>2023.369884664599</v>
       </c>
       <c r="D16">
-        <v>2153.041453299616</v>
+        <v>2158.164884664599</v>
       </c>
       <c r="E16">
-        <v>-559.5579999999999</v>
+        <v>-535.0049999999999</v>
       </c>
       <c r="F16">
-        <v>343.7420000000001</v>
+        <v>368.2950000000001</v>
       </c>
       <c r="G16">
         <v>233.5</v>
@@ -2724,28 +2724,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M16">
-        <v>18.66519060000001</v>
+        <v>19.9984185</v>
       </c>
       <c r="N16">
-        <v>113.6014760666666</v>
+        <v>112.2682481666667</v>
       </c>
       <c r="O16">
-        <v>21.58428045266666</v>
+        <v>21.33096715166666</v>
       </c>
       <c r="P16">
-        <v>92.01719561399999</v>
+        <v>90.937281015</v>
       </c>
       <c r="Q16">
-        <v>146.017195614</v>
+        <v>144.937281015</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09752339811739555</v>
+        <v>0.09802976092665225</v>
       </c>
       <c r="T16">
-        <v>1.008185302018328</v>
+        <v>1.018055255663343</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.086274632880878</v>
+        <v>6.613856324022154</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08992274678765441</v>
+        <v>0.08981775119434865</v>
       </c>
       <c r="C17">
-        <v>2023.369884664599</v>
+        <v>2003.964757883214</v>
       </c>
       <c r="D17">
-        <v>2158.164884664599</v>
+        <v>2163.312757883214</v>
       </c>
       <c r="E17">
-        <v>-535.0049999999999</v>
+        <v>-510.4519999999999</v>
       </c>
       <c r="F17">
-        <v>368.295</v>
+        <v>392.848</v>
       </c>
       <c r="G17">
         <v>233.5</v>
@@ -2806,28 +2806,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M17">
-        <v>19.9984185</v>
+        <v>21.3316464</v>
       </c>
       <c r="N17">
-        <v>112.2682481666667</v>
+        <v>110.9350202666667</v>
       </c>
       <c r="O17">
-        <v>21.33096715166666</v>
+        <v>21.07765385066666</v>
       </c>
       <c r="P17">
-        <v>90.937281015</v>
+        <v>89.85736641599999</v>
       </c>
       <c r="Q17">
-        <v>144.937281015</v>
+        <v>143.857366416</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09802976092665225</v>
+        <v>0.0985481799932722</v>
       </c>
       <c r="T17">
-        <v>1.018055255663343</v>
+        <v>1.028160208204667</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.613856324022155</v>
+        <v>6.20049030377077</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08981775119434865</v>
+        <v>0.08985045560104289</v>
       </c>
       <c r="C18">
-        <v>2003.964757883214</v>
+        <v>1977.805648269242</v>
       </c>
       <c r="D18">
-        <v>2163.312757883214</v>
+        <v>2161.706648269242</v>
       </c>
       <c r="E18">
-        <v>-510.4519999999999</v>
+        <v>-485.8989999999999</v>
       </c>
       <c r="F18">
-        <v>392.848</v>
+        <v>417.4010000000001</v>
       </c>
       <c r="G18">
         <v>233.5</v>
@@ -2888,45 +2888,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M18">
-        <v>21.3316464</v>
+        <v>23.08227530000001</v>
       </c>
       <c r="N18">
-        <v>110.9350202666667</v>
+        <v>109.1843913666666</v>
       </c>
       <c r="O18">
-        <v>21.07765385066666</v>
+        <v>20.74503435966666</v>
       </c>
       <c r="P18">
-        <v>89.85736641599999</v>
+        <v>88.43935700699998</v>
       </c>
       <c r="Q18">
-        <v>143.857366416</v>
+        <v>142.439357007</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0985481799932722</v>
+        <v>0.09907909108559385</v>
       </c>
       <c r="T18">
-        <v>1.028160208204667</v>
+        <v>1.038508653578312</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.19</v>
       </c>
       <c r="W18">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.20049030377077</v>
+        <v>5.73022654602281</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08985045560104289</v>
+        <v>0.08975356000773713</v>
       </c>
       <c r="C19">
-        <v>1977.805648269242</v>
+        <v>1958.018129113119</v>
       </c>
       <c r="D19">
-        <v>2161.706648269242</v>
+        <v>2166.472129113119</v>
       </c>
       <c r="E19">
-        <v>-485.8989999999999</v>
+        <v>-461.3459999999999</v>
       </c>
       <c r="F19">
-        <v>417.4010000000001</v>
+        <v>441.9540000000001</v>
       </c>
       <c r="G19">
         <v>233.5</v>
@@ -2970,28 +2970,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M19">
-        <v>23.08227530000001</v>
+        <v>24.4400562</v>
       </c>
       <c r="N19">
-        <v>109.1843913666666</v>
+        <v>107.8266104666667</v>
       </c>
       <c r="O19">
-        <v>20.74503435966666</v>
+        <v>20.48705598866666</v>
       </c>
       <c r="P19">
-        <v>88.43935700699998</v>
+        <v>87.33955447799998</v>
       </c>
       <c r="Q19">
-        <v>142.439357007</v>
+        <v>141.339554478</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09907909108559385</v>
+        <v>0.09962295122894772</v>
       </c>
       <c r="T19">
-        <v>1.038508653578312</v>
+        <v>1.049109500058632</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.73022654602281</v>
+        <v>5.411880626799321</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08975356000773714</v>
+        <v>0.08965666441443138</v>
       </c>
       <c r="C20">
-        <v>1958.018129113119</v>
+        <v>1938.251667376656</v>
       </c>
       <c r="D20">
-        <v>2166.472129113119</v>
+        <v>2171.258667376656</v>
       </c>
       <c r="E20">
-        <v>-461.3459999999999</v>
+        <v>-436.7929999999999</v>
       </c>
       <c r="F20">
-        <v>441.954</v>
+        <v>466.5070000000001</v>
       </c>
       <c r="G20">
         <v>233.5</v>
@@ -3052,28 +3052,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M20">
-        <v>24.4400562</v>
+        <v>25.79783710000001</v>
       </c>
       <c r="N20">
-        <v>107.8266104666667</v>
+        <v>106.4688295666666</v>
       </c>
       <c r="O20">
-        <v>20.48705598866666</v>
+        <v>20.22907761766666</v>
       </c>
       <c r="P20">
-        <v>87.33955447799998</v>
+        <v>86.23975194899998</v>
       </c>
       <c r="Q20">
-        <v>141.339554478</v>
+        <v>140.239751949</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09962295122894772</v>
+        <v>0.1001802400178165</v>
       </c>
       <c r="T20">
-        <v>1.049109500058632</v>
+        <v>1.059972095834762</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.411880626799322</v>
+        <v>5.127044804336198</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08965666441443138</v>
+        <v>0.08955976882112562</v>
       </c>
       <c r="C21">
-        <v>1938.251667376656</v>
+        <v>1918.506402939787</v>
       </c>
       <c r="D21">
-        <v>2171.258667376656</v>
+        <v>2176.066402939787</v>
       </c>
       <c r="E21">
-        <v>-436.7929999999999</v>
+        <v>-412.2399999999999</v>
       </c>
       <c r="F21">
-        <v>466.5070000000001</v>
+        <v>491.0600000000001</v>
       </c>
       <c r="G21">
         <v>233.5</v>
@@ -3134,28 +3134,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M21">
-        <v>25.79783710000001</v>
+        <v>27.155618</v>
       </c>
       <c r="N21">
-        <v>106.4688295666666</v>
+        <v>105.1110486666666</v>
       </c>
       <c r="O21">
-        <v>20.22907761766666</v>
+        <v>19.97109924666666</v>
       </c>
       <c r="P21">
-        <v>86.23975194899998</v>
+        <v>85.13994941999998</v>
       </c>
       <c r="Q21">
-        <v>140.239751949</v>
+        <v>139.13994942</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1001802400178165</v>
+        <v>0.100751461026407</v>
       </c>
       <c r="T21">
-        <v>1.059972095834762</v>
+        <v>1.071106256505295</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.127044804336198</v>
+        <v>4.870692564119389</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08955976882112562</v>
+        <v>0.08946287322781987</v>
       </c>
       <c r="C22">
-        <v>1918.506402939787</v>
+        <v>1898.782476924117</v>
       </c>
       <c r="D22">
-        <v>2176.066402939787</v>
+        <v>2180.895476924117</v>
       </c>
       <c r="E22">
-        <v>-412.2399999999999</v>
+        <v>-387.6869999999999</v>
       </c>
       <c r="F22">
-        <v>491.0600000000001</v>
+        <v>515.6130000000001</v>
       </c>
       <c r="G22">
         <v>233.5</v>
@@ -3216,28 +3216,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M22">
-        <v>27.155618</v>
+        <v>28.51339890000001</v>
       </c>
       <c r="N22">
-        <v>105.1110486666666</v>
+        <v>103.7532677666667</v>
       </c>
       <c r="O22">
-        <v>19.97109924666666</v>
+        <v>19.71312087566666</v>
       </c>
       <c r="P22">
-        <v>85.13994941999998</v>
+        <v>84.04014689099999</v>
       </c>
       <c r="Q22">
-        <v>139.13994942</v>
+        <v>138.040146891</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.100751461026407</v>
+        <v>0.1013371433263543</v>
       </c>
       <c r="T22">
-        <v>1.071106256505295</v>
+        <v>1.082522294661158</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.870692564119389</v>
+        <v>4.638754822970847</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08946287322781987</v>
+        <v>0.08981147763451411</v>
       </c>
       <c r="C23">
-        <v>1898.782476924117</v>
+        <v>1856.955124535661</v>
       </c>
       <c r="D23">
-        <v>2180.895476924117</v>
+        <v>2163.621124535661</v>
       </c>
       <c r="E23">
-        <v>-387.6869999999999</v>
+        <v>-363.1339999999999</v>
       </c>
       <c r="F23">
-        <v>515.6130000000001</v>
+        <v>540.1660000000001</v>
       </c>
       <c r="G23">
         <v>233.5</v>
@@ -3298,45 +3298,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M23">
-        <v>28.51339890000001</v>
+        <v>31.22159480000001</v>
       </c>
       <c r="N23">
-        <v>103.7532677666667</v>
+        <v>101.0450718666666</v>
       </c>
       <c r="O23">
-        <v>19.71312087566666</v>
+        <v>19.19856365466666</v>
       </c>
       <c r="P23">
-        <v>84.04014689099999</v>
+        <v>81.84650821199997</v>
       </c>
       <c r="Q23">
-        <v>138.040146891</v>
+        <v>135.846508212</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1013371433263543</v>
+        <v>0.1019378431211719</v>
       </c>
       <c r="T23">
-        <v>1.082522294661158</v>
+        <v>1.094231051744095</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.19</v>
       </c>
       <c r="W23">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.638754822970847</v>
+        <v>4.236384064105099</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08981147763451411</v>
+        <v>0.08973483204120836</v>
       </c>
       <c r="C24">
-        <v>1856.955124535661</v>
+        <v>1836.17662456387</v>
       </c>
       <c r="D24">
-        <v>2163.621124535661</v>
+        <v>2167.39562456387</v>
       </c>
       <c r="E24">
-        <v>-363.1339999999999</v>
+        <v>-338.5809999999999</v>
       </c>
       <c r="F24">
-        <v>540.1660000000001</v>
+        <v>564.7190000000001</v>
       </c>
       <c r="G24">
         <v>233.5</v>
@@ -3380,28 +3380,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M24">
-        <v>31.22159480000001</v>
+        <v>32.64075820000001</v>
       </c>
       <c r="N24">
-        <v>101.0450718666666</v>
+        <v>99.62590846666664</v>
       </c>
       <c r="O24">
-        <v>19.19856365466666</v>
+        <v>18.92892260866666</v>
       </c>
       <c r="P24">
-        <v>81.84650821199997</v>
+        <v>80.69698585799998</v>
       </c>
       <c r="Q24">
-        <v>135.846508212</v>
+        <v>134.696985858</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1019378431211719</v>
+        <v>0.1025541455080628</v>
       </c>
       <c r="T24">
-        <v>1.094231051744095</v>
+        <v>1.106243932387627</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.236384064105099</v>
+        <v>4.052193452622268</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08973483204120836</v>
+        <v>0.09033858644790259</v>
       </c>
       <c r="C25">
-        <v>1836.17662456387</v>
+        <v>1782.242928773021</v>
       </c>
       <c r="D25">
-        <v>2167.39562456387</v>
+        <v>2138.014928773021</v>
       </c>
       <c r="E25">
-        <v>-338.5809999999999</v>
+        <v>-314.0279999999999</v>
       </c>
       <c r="F25">
-        <v>564.7190000000001</v>
+        <v>589.272</v>
       </c>
       <c r="G25">
         <v>233.5</v>
@@ -3462,45 +3462,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M25">
-        <v>32.64075820000001</v>
+        <v>36.1223736</v>
       </c>
       <c r="N25">
-        <v>99.62590846666664</v>
+        <v>96.14429306666665</v>
       </c>
       <c r="O25">
-        <v>18.92892260866666</v>
+        <v>18.26741568266666</v>
       </c>
       <c r="P25">
-        <v>80.69698585799998</v>
+        <v>77.87687738399998</v>
       </c>
       <c r="Q25">
-        <v>134.696985858</v>
+        <v>131.876877384</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1025541455080628</v>
+        <v>0.1031866663788192</v>
       </c>
       <c r="T25">
-        <v>1.106243932387627</v>
+        <v>1.118572941469147</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.19</v>
       </c>
       <c r="W25">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.052193452622268</v>
+        <v>3.661627226696604</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09033858644790259</v>
+        <v>0.09029029085459685</v>
       </c>
       <c r="C26">
-        <v>1782.242928773021</v>
+        <v>1760.010810419291</v>
       </c>
       <c r="D26">
-        <v>2138.014928773021</v>
+        <v>2140.335810419291</v>
       </c>
       <c r="E26">
-        <v>-314.0279999999999</v>
+        <v>-289.4749999999999</v>
       </c>
       <c r="F26">
-        <v>589.272</v>
+        <v>613.825</v>
       </c>
       <c r="G26">
         <v>233.5</v>
@@ -3544,28 +3544,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M26">
-        <v>36.1223736</v>
+        <v>37.6274725</v>
       </c>
       <c r="N26">
-        <v>96.14429306666665</v>
+        <v>94.63919416666664</v>
       </c>
       <c r="O26">
-        <v>18.26741568266666</v>
+        <v>17.98144689166666</v>
       </c>
       <c r="P26">
-        <v>77.87687738399998</v>
+        <v>76.65774727499998</v>
       </c>
       <c r="Q26">
-        <v>131.876877384</v>
+        <v>130.657747275</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1031866663788192</v>
+        <v>0.1038360544727958</v>
       </c>
       <c r="T26">
-        <v>1.118572941469147</v>
+        <v>1.131230724126174</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.661627226696604</v>
+        <v>3.51516213762874</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09029029085459685</v>
+        <v>0.09083167526129109</v>
       </c>
       <c r="C27">
-        <v>1760.010810419291</v>
+        <v>1709.726046585793</v>
       </c>
       <c r="D27">
-        <v>2140.335810419291</v>
+        <v>2114.604046585793</v>
       </c>
       <c r="E27">
-        <v>-289.4749999999999</v>
+        <v>-264.9219999999999</v>
       </c>
       <c r="F27">
-        <v>613.825</v>
+        <v>638.378</v>
       </c>
       <c r="G27">
         <v>233.5</v>
@@ -3626,45 +3626,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M27">
-        <v>37.6274725</v>
+        <v>40.92002980000001</v>
       </c>
       <c r="N27">
-        <v>94.63919416666664</v>
+        <v>91.34663686666664</v>
       </c>
       <c r="O27">
-        <v>17.98144689166666</v>
+        <v>17.35586100466666</v>
       </c>
       <c r="P27">
-        <v>76.65774727499998</v>
+        <v>73.99077586199998</v>
       </c>
       <c r="Q27">
-        <v>130.657747275</v>
+        <v>127.990775862</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1038360544727958</v>
+        <v>0.1045029935963393</v>
       </c>
       <c r="T27">
-        <v>1.131230724126174</v>
+        <v>1.144230609017175</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.19</v>
       </c>
       <c r="W27">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.51516213762874</v>
+        <v>3.232320878384761</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09083167526129109</v>
+        <v>0.0908060596679853</v>
       </c>
       <c r="C28">
-        <v>1709.726046585793</v>
+        <v>1686.376592011892</v>
       </c>
       <c r="D28">
-        <v>2114.604046585793</v>
+        <v>2115.807592011892</v>
       </c>
       <c r="E28">
-        <v>-264.9219999999999</v>
+        <v>-240.3689999999999</v>
       </c>
       <c r="F28">
-        <v>638.378</v>
+        <v>662.931</v>
       </c>
       <c r="G28">
         <v>233.5</v>
@@ -3708,28 +3708,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M28">
-        <v>40.92002980000001</v>
+        <v>42.49387710000001</v>
       </c>
       <c r="N28">
-        <v>91.34663686666664</v>
+        <v>89.77278956666665</v>
       </c>
       <c r="O28">
-        <v>17.35586100466666</v>
+        <v>17.05683001766666</v>
       </c>
       <c r="P28">
-        <v>73.99077586199998</v>
+        <v>72.71595954899999</v>
       </c>
       <c r="Q28">
-        <v>127.990775862</v>
+        <v>126.715959549</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1045029935963393</v>
+        <v>0.1051882050246374</v>
       </c>
       <c r="T28">
-        <v>1.144230609017175</v>
+        <v>1.157586655138066</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.232320878384761</v>
+        <v>3.112605290296437</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0908060596679853</v>
+        <v>0.09078044407467956</v>
       </c>
       <c r="C29">
-        <v>1686.376592011892</v>
+        <v>1663.028508235044</v>
       </c>
       <c r="D29">
-        <v>2115.807592011892</v>
+        <v>2117.012508235044</v>
       </c>
       <c r="E29">
-        <v>-240.3689999999999</v>
+        <v>-215.8159999999998</v>
       </c>
       <c r="F29">
-        <v>662.931</v>
+        <v>687.4840000000002</v>
       </c>
       <c r="G29">
         <v>233.5</v>
@@ -3790,28 +3790,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M29">
-        <v>42.49387710000001</v>
+        <v>44.06772440000001</v>
       </c>
       <c r="N29">
-        <v>89.77278956666665</v>
+        <v>88.19894226666665</v>
       </c>
       <c r="O29">
-        <v>17.05683001766666</v>
+        <v>16.75779903066666</v>
       </c>
       <c r="P29">
-        <v>72.71595954899999</v>
+        <v>71.44114323599999</v>
       </c>
       <c r="Q29">
-        <v>126.715959549</v>
+        <v>125.441143236</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1051882050246374</v>
+        <v>0.1058924501037216</v>
       </c>
       <c r="T29">
-        <v>1.157586655138066</v>
+        <v>1.171313702540094</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.112605290296437</v>
+        <v>3.001440815642993</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09078044407467956</v>
+        <v>0.09258704848137381</v>
       </c>
       <c r="C30">
-        <v>1663.028508235044</v>
+        <v>1556.730575597823</v>
       </c>
       <c r="D30">
-        <v>2117.012508235044</v>
+        <v>2035.267575597823</v>
       </c>
       <c r="E30">
-        <v>-215.8159999999998</v>
+        <v>-191.2629999999998</v>
       </c>
       <c r="F30">
-        <v>687.4840000000002</v>
+        <v>712.0370000000001</v>
       </c>
       <c r="G30">
         <v>233.5</v>
@@ -3872,45 +3872,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M30">
-        <v>44.06772440000001</v>
+        <v>51.19546030000001</v>
       </c>
       <c r="N30">
-        <v>88.19894226666665</v>
+        <v>81.07120636666664</v>
       </c>
       <c r="O30">
-        <v>16.75779903066666</v>
+        <v>15.40352920966666</v>
       </c>
       <c r="P30">
-        <v>71.44114323599999</v>
+        <v>65.66767715699999</v>
       </c>
       <c r="Q30">
-        <v>125.441143236</v>
+        <v>119.667677157</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1058924501037216</v>
+        <v>0.1066165330723575</v>
       </c>
       <c r="T30">
-        <v>1.171313702540094</v>
+        <v>1.185427427333728</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.19</v>
       </c>
       <c r="W30">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.001440815642993</v>
+        <v>2.583562407518126</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09258704848137381</v>
+        <v>0.09357231288806804</v>
       </c>
       <c r="C31">
-        <v>1556.730575597823</v>
+        <v>1490.201866675506</v>
       </c>
       <c r="D31">
-        <v>2035.267575597823</v>
+        <v>1993.291866675506</v>
       </c>
       <c r="E31">
-        <v>-191.2629999999999</v>
+        <v>-166.7099999999999</v>
       </c>
       <c r="F31">
-        <v>712.037</v>
+        <v>736.59</v>
       </c>
       <c r="G31">
         <v>233.5</v>
@@ -3954,45 +3954,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M31">
-        <v>51.19546030000001</v>
+        <v>55.83352200000001</v>
       </c>
       <c r="N31">
-        <v>81.07120636666664</v>
+        <v>76.43314466666664</v>
       </c>
       <c r="O31">
-        <v>15.40352920966666</v>
+        <v>14.52229748666666</v>
       </c>
       <c r="P31">
-        <v>65.66767715699999</v>
+        <v>61.91084717999998</v>
       </c>
       <c r="Q31">
-        <v>119.667677157</v>
+        <v>115.91084718</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1066165330723575</v>
+        <v>0.1073613041258115</v>
       </c>
       <c r="T31">
-        <v>1.185427427333727</v>
+        <v>1.199944401407179</v>
       </c>
       <c r="U31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.19</v>
       </c>
       <c r="W31">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.583562407518126</v>
+        <v>2.368947218960441</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09357231288806804</v>
+        <v>0.09364146729476229</v>
       </c>
       <c r="C32">
-        <v>1490.201866675506</v>
+        <v>1462.767581376309</v>
       </c>
       <c r="D32">
-        <v>1993.291866675506</v>
+        <v>1990.410581376309</v>
       </c>
       <c r="E32">
-        <v>-166.7099999999999</v>
+        <v>-142.1569999999999</v>
       </c>
       <c r="F32">
-        <v>736.59</v>
+        <v>761.143</v>
       </c>
       <c r="G32">
         <v>233.5</v>
@@ -4036,28 +4036,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M32">
-        <v>55.83352200000001</v>
+        <v>57.69463940000001</v>
       </c>
       <c r="N32">
-        <v>76.43314466666664</v>
+        <v>74.57202726666665</v>
       </c>
       <c r="O32">
-        <v>14.52229748666666</v>
+        <v>14.16868518066666</v>
       </c>
       <c r="P32">
-        <v>61.91084717999998</v>
+        <v>60.40334208599999</v>
       </c>
       <c r="Q32">
-        <v>115.91084718</v>
+        <v>114.403342086</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1073613041258115</v>
+        <v>0.1081276627460323</v>
       </c>
       <c r="T32">
-        <v>1.199944401407179</v>
+        <v>1.214882157337833</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.368947218960441</v>
+        <v>2.292529566735912</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09364146729476229</v>
+        <v>0.09371062170145653</v>
       </c>
       <c r="C33">
-        <v>1462.767581376309</v>
+        <v>1435.341613797414</v>
       </c>
       <c r="D33">
-        <v>1990.410581376309</v>
+        <v>1987.537613797414</v>
       </c>
       <c r="E33">
-        <v>-142.1569999999999</v>
+        <v>-117.6039999999999</v>
       </c>
       <c r="F33">
-        <v>761.143</v>
+        <v>785.696</v>
       </c>
       <c r="G33">
         <v>233.5</v>
@@ -4118,28 +4118,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M33">
-        <v>57.69463940000001</v>
+        <v>59.5557568</v>
       </c>
       <c r="N33">
-        <v>74.57202726666665</v>
+        <v>72.71090986666664</v>
       </c>
       <c r="O33">
-        <v>14.16868518066666</v>
+        <v>13.81507287466666</v>
       </c>
       <c r="P33">
-        <v>60.40334208599999</v>
+        <v>58.89583699199998</v>
       </c>
       <c r="Q33">
-        <v>114.403342086</v>
+        <v>112.895836992</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1081276627460323</v>
+        <v>0.1089165613256714</v>
       </c>
       <c r="T33">
-        <v>1.214882157337833</v>
+        <v>1.230259259031152</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.292529566735912</v>
+        <v>2.220888017775414</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09371062170145653</v>
+        <v>0.09377977610815078</v>
       </c>
       <c r="C34">
-        <v>1435.341613797414</v>
+        <v>1407.923927973227</v>
       </c>
       <c r="D34">
-        <v>1987.537613797414</v>
+        <v>1984.672927973227</v>
       </c>
       <c r="E34">
-        <v>-117.6039999999999</v>
+        <v>-93.05099999999982</v>
       </c>
       <c r="F34">
-        <v>785.696</v>
+        <v>810.2490000000001</v>
       </c>
       <c r="G34">
         <v>233.5</v>
@@ -4200,28 +4200,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M34">
-        <v>59.5557568</v>
+        <v>61.41687420000002</v>
       </c>
       <c r="N34">
-        <v>72.71090986666664</v>
+        <v>70.84979246666663</v>
       </c>
       <c r="O34">
-        <v>13.81507287466666</v>
+        <v>13.46146056866666</v>
       </c>
       <c r="P34">
-        <v>58.89583699199998</v>
+        <v>57.38833189799997</v>
       </c>
       <c r="Q34">
-        <v>112.895836992</v>
+        <v>111.388331898</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1089165613256714</v>
+        <v>0.109729009116643</v>
       </c>
       <c r="T34">
-        <v>1.230259259031152</v>
+        <v>1.246095378685466</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.220888017775414</v>
+        <v>2.153588380873129</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09377977610815078</v>
+        <v>0.09384893051484501</v>
       </c>
       <c r="C35">
-        <v>1407.923927973227</v>
+        <v>1380.514488145213</v>
       </c>
       <c r="D35">
-        <v>1984.672927973227</v>
+        <v>1981.816488145213</v>
       </c>
       <c r="E35">
-        <v>-93.05099999999982</v>
+        <v>-68.49799999999982</v>
       </c>
       <c r="F35">
-        <v>810.2490000000001</v>
+        <v>834.8020000000001</v>
       </c>
       <c r="G35">
         <v>233.5</v>
@@ -4282,28 +4282,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M35">
-        <v>61.41687420000002</v>
+        <v>63.27799160000001</v>
       </c>
       <c r="N35">
-        <v>70.84979246666663</v>
+        <v>68.98867506666664</v>
       </c>
       <c r="O35">
-        <v>13.46146056866666</v>
+        <v>13.10784826266666</v>
       </c>
       <c r="P35">
-        <v>57.38833189799997</v>
+        <v>55.88082680399998</v>
       </c>
       <c r="Q35">
-        <v>111.388331898</v>
+        <v>109.880826804</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.109729009116643</v>
+        <v>0.110566076537644</v>
       </c>
       <c r="T35">
-        <v>1.246095378685466</v>
+        <v>1.262411380753548</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.153588380873129</v>
+        <v>2.090247546141566</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09384893051484501</v>
+        <v>0.09391808492153925</v>
       </c>
       <c r="C36">
-        <v>1380.514488145213</v>
+        <v>1353.113258760398</v>
       </c>
       <c r="D36">
-        <v>1981.816488145213</v>
+        <v>1978.968258760398</v>
       </c>
       <c r="E36">
-        <v>-68.49799999999982</v>
+        <v>-43.94499999999982</v>
       </c>
       <c r="F36">
-        <v>834.8020000000001</v>
+        <v>859.3550000000001</v>
       </c>
       <c r="G36">
         <v>233.5</v>
@@ -4364,28 +4364,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M36">
-        <v>63.27799160000001</v>
+        <v>65.13910900000002</v>
       </c>
       <c r="N36">
-        <v>68.98867506666664</v>
+        <v>67.12755766666663</v>
       </c>
       <c r="O36">
-        <v>13.10784826266666</v>
+        <v>12.75423595666666</v>
       </c>
       <c r="P36">
-        <v>55.88082680399998</v>
+        <v>54.37332170999997</v>
       </c>
       <c r="Q36">
-        <v>109.880826804</v>
+        <v>108.37332171</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.110566076537644</v>
+        <v>0.1114288998792912</v>
       </c>
       <c r="T36">
-        <v>1.262411380753548</v>
+        <v>1.279229413654493</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.090247546141566</v>
+        <v>2.030526187680378</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09391808492153925</v>
+        <v>0.0981279593282335</v>
       </c>
       <c r="C37">
-        <v>1353.113258760398</v>
+        <v>1169.348855694646</v>
       </c>
       <c r="D37">
-        <v>1978.968258760398</v>
+        <v>1819.756855694646</v>
       </c>
       <c r="E37">
-        <v>-43.94499999999982</v>
+        <v>-19.39199999999983</v>
       </c>
       <c r="F37">
-        <v>859.3550000000001</v>
+        <v>883.9080000000001</v>
       </c>
       <c r="G37">
         <v>233.5</v>
@@ -4446,45 +4446,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M37">
-        <v>65.13910900000002</v>
+        <v>79.55172</v>
       </c>
       <c r="N37">
-        <v>67.12755766666663</v>
+        <v>52.71494666666665</v>
       </c>
       <c r="O37">
-        <v>12.75423595666666</v>
+        <v>10.01583986666666</v>
       </c>
       <c r="P37">
-        <v>54.37332170999997</v>
+        <v>42.69910679999998</v>
       </c>
       <c r="Q37">
-        <v>108.37332171</v>
+        <v>96.69910679999998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1114288998792912</v>
+        <v>0.1123186864503649</v>
       </c>
       <c r="T37">
-        <v>1.279229413654493</v>
+        <v>1.296573010083593</v>
       </c>
       <c r="U37">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V37">
         <v>0.19</v>
       </c>
       <c r="W37">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.030526187680378</v>
+        <v>1.66264999256668</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0981279593282335</v>
+        <v>0.09831213373492774</v>
       </c>
       <c r="C38">
-        <v>1169.348855694646</v>
+        <v>1138.41347098872</v>
       </c>
       <c r="D38">
-        <v>1819.756855694646</v>
+        <v>1813.37447098872</v>
       </c>
       <c r="E38">
-        <v>-19.39199999999994</v>
+        <v>5.161000000000058</v>
       </c>
       <c r="F38">
-        <v>883.908</v>
+        <v>908.461</v>
       </c>
       <c r="G38">
         <v>233.5</v>
@@ -4528,28 +4528,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M38">
-        <v>79.55172</v>
+        <v>81.76148999999999</v>
       </c>
       <c r="N38">
-        <v>52.71494666666665</v>
+        <v>50.50517666666666</v>
       </c>
       <c r="O38">
-        <v>10.01583986666666</v>
+        <v>9.595983566666664</v>
       </c>
       <c r="P38">
-        <v>42.69910679999998</v>
+        <v>40.9091931</v>
       </c>
       <c r="Q38">
-        <v>96.69910679999998</v>
+        <v>94.9091931</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1123186864503648</v>
+        <v>0.113236720214171</v>
       </c>
       <c r="T38">
-        <v>1.296573010083592</v>
+        <v>1.314467196875521</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.66264999256668</v>
+        <v>1.617713506281095</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09831213373492774</v>
+        <v>0.098496308141622</v>
       </c>
       <c r="C39">
-        <v>1138.41347098872</v>
+        <v>1107.522699348033</v>
       </c>
       <c r="D39">
-        <v>1813.37447098872</v>
+        <v>1807.036699348033</v>
       </c>
       <c r="E39">
-        <v>5.161000000000058</v>
+        <v>29.71400000000017</v>
       </c>
       <c r="F39">
-        <v>908.461</v>
+        <v>933.0140000000001</v>
       </c>
       <c r="G39">
         <v>233.5</v>
@@ -4610,28 +4610,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M39">
-        <v>81.76148999999999</v>
+        <v>83.97126000000002</v>
       </c>
       <c r="N39">
-        <v>50.50517666666666</v>
+        <v>48.29540666666664</v>
       </c>
       <c r="O39">
-        <v>9.595983566666664</v>
+        <v>9.176127266666661</v>
       </c>
       <c r="P39">
-        <v>40.9091931</v>
+        <v>39.11927939999998</v>
       </c>
       <c r="Q39">
-        <v>94.9091931</v>
+        <v>93.11927939999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.113236720214171</v>
+        <v>0.1141843679703581</v>
       </c>
       <c r="T39">
-        <v>1.314467196875521</v>
+        <v>1.332938615499447</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.617713506281095</v>
+        <v>1.575142098221066</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.098496308141622</v>
+        <v>0.09868048254831624</v>
       </c>
       <c r="C40">
-        <v>1107.522699348033</v>
+        <v>1076.67607463171</v>
       </c>
       <c r="D40">
-        <v>1807.036699348033</v>
+        <v>1800.743074631711</v>
       </c>
       <c r="E40">
-        <v>29.71400000000017</v>
+        <v>54.26700000000017</v>
       </c>
       <c r="F40">
-        <v>933.0140000000001</v>
+        <v>957.5670000000001</v>
       </c>
       <c r="G40">
         <v>233.5</v>
@@ -4692,28 +4692,28 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M40">
-        <v>83.97126000000002</v>
+        <v>86.18103000000001</v>
       </c>
       <c r="N40">
-        <v>48.29540666666664</v>
+        <v>46.08563666666664</v>
       </c>
       <c r="O40">
-        <v>9.176127266666661</v>
+        <v>8.756270966666662</v>
       </c>
       <c r="P40">
-        <v>39.11927939999998</v>
+        <v>37.32936569999998</v>
       </c>
       <c r="Q40">
-        <v>93.11927939999998</v>
+        <v>91.32936569999998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1141843679703581</v>
+        <v>0.1151630861447807</v>
       </c>
       <c r="T40">
-        <v>1.332938615499447</v>
+        <v>1.352015654406125</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.575142098221066</v>
+        <v>1.53475383929232</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09868048254831624</v>
+        <v>0.1184762475680908</v>
       </c>
       <c r="C41">
-        <v>1076.67607463171</v>
+        <v>561.6315047003129</v>
       </c>
       <c r="D41">
-        <v>1800.743074631711</v>
+        <v>1310.251504700313</v>
       </c>
       <c r="E41">
-        <v>54.26700000000017</v>
+        <v>78.82000000000016</v>
       </c>
       <c r="F41">
-        <v>957.5670000000001</v>
+        <v>982.1200000000001</v>
       </c>
       <c r="G41">
         <v>233.5</v>
@@ -4774,45 +4774,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M41">
-        <v>86.18103000000001</v>
+        <v>144.175216</v>
       </c>
       <c r="N41">
-        <v>46.08563666666664</v>
+        <v>-11.90854933333338</v>
       </c>
       <c r="O41">
-        <v>8.756270966666662</v>
+        <v>-2.262624373333343</v>
       </c>
       <c r="P41">
-        <v>37.32936569999998</v>
+        <v>-9.645924960000041</v>
       </c>
       <c r="Q41">
-        <v>91.32936569999998</v>
+        <v>44.35407503999996</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1151630861447807</v>
+        <v>0.1166525348705522</v>
       </c>
       <c r="T41">
-        <v>1.352015654406125</v>
+        <v>1.381047782380867</v>
       </c>
       <c r="U41">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.19</v>
+        <v>0.1743064263324333</v>
       </c>
       <c r="W41">
-        <v>0.07290000000000001</v>
+        <v>0.1212118166143988</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.53475383929232</v>
+        <v>0.9174022438549121</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1184762475680908</v>
+        <v>0.1194862475680908</v>
       </c>
       <c r="C42">
-        <v>561.6315047003129</v>
+        <v>519.1191966418525</v>
       </c>
       <c r="D42">
-        <v>1310.251504700313</v>
+        <v>1292.292196641853</v>
       </c>
       <c r="E42">
-        <v>78.82000000000016</v>
+        <v>103.3730000000002</v>
       </c>
       <c r="F42">
-        <v>982.1200000000001</v>
+        <v>1006.673</v>
       </c>
       <c r="G42">
         <v>233.5</v>
@@ -4856,37 +4856,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M42">
-        <v>144.175216</v>
+        <v>147.7795964</v>
       </c>
       <c r="N42">
-        <v>-11.90854933333338</v>
+        <v>-15.51292973333338</v>
       </c>
       <c r="O42">
-        <v>-2.262624373333343</v>
+        <v>-2.947456649333342</v>
       </c>
       <c r="P42">
-        <v>-9.645924960000041</v>
+        <v>-12.56547308400004</v>
       </c>
       <c r="Q42">
-        <v>44.35407503999996</v>
+        <v>41.43452691599996</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1166525348705522</v>
+        <v>0.117853425292087</v>
       </c>
       <c r="T42">
-        <v>1.381047782380867</v>
+        <v>1.404455371912746</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1743064263324333</v>
+        <v>0.1700550500804227</v>
       </c>
       <c r="W42">
-        <v>0.1212118166143988</v>
+        <v>0.1218359186481939</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.9174022438549121</v>
+        <v>0.895026579370646</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1194862475680908</v>
+        <v>0.1204962475680909</v>
       </c>
       <c r="C43">
-        <v>519.1191966418525</v>
+        <v>477.0925595971205</v>
       </c>
       <c r="D43">
-        <v>1292.292196641853</v>
+        <v>1274.818559597121</v>
       </c>
       <c r="E43">
-        <v>103.3730000000002</v>
+        <v>127.9260000000002</v>
       </c>
       <c r="F43">
-        <v>1006.673</v>
+        <v>1031.226</v>
       </c>
       <c r="G43">
         <v>233.5</v>
@@ -4938,37 +4938,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M43">
-        <v>147.7795964</v>
+        <v>151.3839768</v>
       </c>
       <c r="N43">
-        <v>-15.51292973333338</v>
+        <v>-19.11731013333338</v>
       </c>
       <c r="O43">
-        <v>-2.947456649333342</v>
+        <v>-3.632288925333341</v>
       </c>
       <c r="P43">
-        <v>-12.56547308400004</v>
+        <v>-15.48502120800003</v>
       </c>
       <c r="Q43">
-        <v>41.43452691599996</v>
+        <v>38.51497879199997</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.117853425292087</v>
+        <v>0.1190957257281575</v>
       </c>
       <c r="T43">
-        <v>1.404455371912746</v>
+        <v>1.428670119704345</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1700550500804227</v>
+        <v>0.1660061203166031</v>
       </c>
       <c r="W43">
-        <v>0.1218359186481939</v>
+        <v>0.1224303015375227</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.895026579370646</v>
+        <v>0.8737164227189639</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1204962475680909</v>
+        <v>0.1215062475680909</v>
       </c>
       <c r="C44">
-        <v>477.0925595971205</v>
+        <v>435.5321554983364</v>
       </c>
       <c r="D44">
-        <v>1274.818559597121</v>
+        <v>1257.811155498336</v>
       </c>
       <c r="E44">
-        <v>127.9260000000002</v>
+        <v>152.479</v>
       </c>
       <c r="F44">
-        <v>1031.226</v>
+        <v>1055.779</v>
       </c>
       <c r="G44">
         <v>233.5</v>
@@ -5020,37 +5020,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M44">
-        <v>151.3839768</v>
+        <v>154.9883572</v>
       </c>
       <c r="N44">
-        <v>-19.11731013333338</v>
+        <v>-22.72169053333337</v>
       </c>
       <c r="O44">
-        <v>-3.632288925333341</v>
+        <v>-4.31712120133334</v>
       </c>
       <c r="P44">
-        <v>-15.48502120800003</v>
+        <v>-18.40456933200003</v>
       </c>
       <c r="Q44">
-        <v>38.51497879199997</v>
+        <v>35.59543066799996</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1190957257281575</v>
+        <v>0.1203816156532129</v>
       </c>
       <c r="T44">
-        <v>1.428670119704345</v>
+        <v>1.453734507769334</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1660061203166031</v>
+        <v>0.1621455128673798</v>
       </c>
       <c r="W44">
-        <v>0.1224303015375227</v>
+        <v>0.1229970387110687</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8737164227189639</v>
+        <v>0.8533974361441043</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1215062475680909</v>
+        <v>0.1225162475680908</v>
       </c>
       <c r="C45">
-        <v>435.5321554983364</v>
+        <v>394.419569917384</v>
       </c>
       <c r="D45">
-        <v>1257.811155498336</v>
+        <v>1241.251569917384</v>
       </c>
       <c r="E45">
-        <v>152.479</v>
+        <v>177.0320000000002</v>
       </c>
       <c r="F45">
-        <v>1055.779</v>
+        <v>1080.332</v>
       </c>
       <c r="G45">
         <v>233.5</v>
@@ -5102,37 +5102,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M45">
-        <v>154.9883572</v>
+        <v>158.5927376</v>
       </c>
       <c r="N45">
-        <v>-22.72169053333337</v>
+        <v>-26.32607093333337</v>
       </c>
       <c r="O45">
-        <v>-4.31712120133334</v>
+        <v>-5.00195347733334</v>
       </c>
       <c r="P45">
-        <v>-18.40456933200003</v>
+        <v>-21.32411745600003</v>
       </c>
       <c r="Q45">
-        <v>35.59543066799996</v>
+        <v>32.67588254399998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1203816156532129</v>
+        <v>0.1217134302184488</v>
       </c>
       <c r="T45">
-        <v>1.453734507769334</v>
+        <v>1.479694052550929</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1621455128673798</v>
+        <v>0.1584603875749394</v>
       </c>
       <c r="W45">
-        <v>0.1229970387110687</v>
+        <v>0.1235380151039989</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8533974361441043</v>
+        <v>0.834002039868102</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1225162475680908</v>
+        <v>0.1235262475680909</v>
       </c>
       <c r="C46">
-        <v>394.419569917384</v>
+        <v>353.7373455582858</v>
       </c>
       <c r="D46">
-        <v>1241.251569917384</v>
+        <v>1225.122345558286</v>
       </c>
       <c r="E46">
-        <v>177.0320000000002</v>
+        <v>201.5850000000003</v>
       </c>
       <c r="F46">
-        <v>1080.332</v>
+        <v>1104.885</v>
       </c>
       <c r="G46">
         <v>233.5</v>
@@ -5184,37 +5184,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M46">
-        <v>158.5927376</v>
+        <v>162.197118</v>
       </c>
       <c r="N46">
-        <v>-26.32607093333337</v>
+        <v>-29.93045133333339</v>
       </c>
       <c r="O46">
-        <v>-5.00195347733334</v>
+        <v>-5.686785753333345</v>
       </c>
       <c r="P46">
-        <v>-21.32411745600003</v>
+        <v>-24.24366558000005</v>
       </c>
       <c r="Q46">
-        <v>32.67588254399998</v>
+        <v>29.75633441999995</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1217134302184488</v>
+        <v>0.1230936744042388</v>
       </c>
       <c r="T46">
-        <v>1.479694052550929</v>
+        <v>1.506597580779127</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1584603875749394</v>
+        <v>0.1549390456288296</v>
       </c>
       <c r="W46">
-        <v>0.1235380151039989</v>
+        <v>0.1240549481016878</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.834002039868102</v>
+        <v>0.8154686612043662</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1235262475680909</v>
+        <v>0.150233083361443</v>
       </c>
       <c r="C47">
-        <v>353.7373455582858</v>
+        <v>15.88189142743704</v>
       </c>
       <c r="D47">
-        <v>1225.122345558286</v>
+        <v>911.8198914274371</v>
       </c>
       <c r="E47">
-        <v>201.5850000000003</v>
+        <v>226.1380000000001</v>
       </c>
       <c r="F47">
-        <v>1104.885</v>
+        <v>1129.438</v>
       </c>
       <c r="G47">
         <v>233.5</v>
@@ -5266,45 +5266,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M47">
-        <v>162.197118</v>
+        <v>226.7911504</v>
       </c>
       <c r="N47">
-        <v>-29.93045133333339</v>
+        <v>-94.52448373333337</v>
       </c>
       <c r="O47">
-        <v>-5.686785753333345</v>
+        <v>-17.95965190933334</v>
       </c>
       <c r="P47">
-        <v>-24.24366558000005</v>
+        <v>-76.56483182400002</v>
       </c>
       <c r="Q47">
-        <v>29.75633441999995</v>
+        <v>-22.56483182400002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1230936744042388</v>
+        <v>0.1261117716957101</v>
       </c>
       <c r="T47">
-        <v>1.506597580779127</v>
+        <v>1.565425914571439</v>
       </c>
       <c r="U47">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1549390456288296</v>
+        <v>0.1108097323124944</v>
       </c>
       <c r="W47">
-        <v>0.1240549481016878</v>
+        <v>0.1785494057516512</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.8154686612043662</v>
+        <v>0.5832091174341811</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.150233083361443</v>
+        <v>0.151783083361443</v>
       </c>
       <c r="C48">
-        <v>15.88189142743704</v>
+        <v>-22.00645216596035</v>
       </c>
       <c r="D48">
-        <v>911.8198914274371</v>
+        <v>898.48454783404</v>
       </c>
       <c r="E48">
-        <v>226.1380000000001</v>
+        <v>250.6910000000003</v>
       </c>
       <c r="F48">
-        <v>1129.438</v>
+        <v>1153.991</v>
       </c>
       <c r="G48">
         <v>233.5</v>
@@ -5348,37 +5348,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M48">
-        <v>226.7911504</v>
+        <v>231.7213928</v>
       </c>
       <c r="N48">
-        <v>-94.52448373333337</v>
+        <v>-99.45472613333339</v>
       </c>
       <c r="O48">
-        <v>-17.95965190933334</v>
+        <v>-18.89639796533335</v>
       </c>
       <c r="P48">
-        <v>-76.56483182400002</v>
+        <v>-80.55832816800005</v>
       </c>
       <c r="Q48">
-        <v>-22.56483182400002</v>
+        <v>-26.55832816800005</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1261117716957101</v>
+        <v>0.127627088142799</v>
       </c>
       <c r="T48">
-        <v>1.565425914571439</v>
+        <v>1.59496225258222</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1108097323124944</v>
+        <v>0.1084520784335052</v>
       </c>
       <c r="W48">
-        <v>0.1785494057516512</v>
+        <v>0.1790228226505522</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5832091174341811</v>
+        <v>0.5708004128079219</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.151783083361443</v>
+        <v>0.153333083361443</v>
       </c>
       <c r="C49">
-        <v>-22.00645216596035</v>
+        <v>-59.51035997599433</v>
       </c>
       <c r="D49">
-        <v>898.48454783404</v>
+        <v>885.5336400240059</v>
       </c>
       <c r="E49">
-        <v>250.6910000000003</v>
+        <v>275.2440000000001</v>
       </c>
       <c r="F49">
-        <v>1153.991</v>
+        <v>1178.544</v>
       </c>
       <c r="G49">
         <v>233.5</v>
@@ -5430,37 +5430,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M49">
-        <v>231.7213928</v>
+        <v>236.6516352</v>
       </c>
       <c r="N49">
-        <v>-99.45472613333339</v>
+        <v>-104.3849685333334</v>
       </c>
       <c r="O49">
-        <v>-18.89639796533335</v>
+        <v>-19.83314402133334</v>
       </c>
       <c r="P49">
-        <v>-80.55832816800005</v>
+        <v>-84.55182451200002</v>
       </c>
       <c r="Q49">
-        <v>-26.55832816800005</v>
+        <v>-30.55182451200002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.127627088142799</v>
+        <v>0.129200685991699</v>
       </c>
       <c r="T49">
-        <v>1.59496225258222</v>
+        <v>1.625634603593417</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1084520784335052</v>
+        <v>0.1061926601328071</v>
       </c>
       <c r="W49">
-        <v>0.1790228226505522</v>
+        <v>0.1794765138453323</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5708004128079219</v>
+        <v>0.5589087375410903</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.153333083361443</v>
+        <v>0.154883083361443</v>
       </c>
       <c r="C50">
-        <v>-59.51035997599433</v>
+        <v>-96.64621975351997</v>
       </c>
       <c r="D50">
-        <v>885.5336400240059</v>
+        <v>872.9507802464801</v>
       </c>
       <c r="E50">
-        <v>275.2440000000001</v>
+        <v>299.797</v>
       </c>
       <c r="F50">
-        <v>1178.544</v>
+        <v>1203.097</v>
       </c>
       <c r="G50">
         <v>233.5</v>
@@ -5512,37 +5512,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M50">
-        <v>236.6516352</v>
+        <v>241.5818776</v>
       </c>
       <c r="N50">
-        <v>-104.3849685333334</v>
+        <v>-109.3152109333334</v>
       </c>
       <c r="O50">
-        <v>-19.83314402133334</v>
+        <v>-20.76989007733334</v>
       </c>
       <c r="P50">
-        <v>-84.55182451200002</v>
+        <v>-88.54532085600002</v>
       </c>
       <c r="Q50">
-        <v>-30.55182451200002</v>
+        <v>-34.54532085600002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.129200685991699</v>
+        <v>0.1308359935601636</v>
       </c>
       <c r="T50">
-        <v>1.625634603593417</v>
+        <v>1.65750979189917</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1061926601328071</v>
+        <v>0.1040254629872397</v>
       </c>
       <c r="W50">
-        <v>0.1794765138453323</v>
+        <v>0.1799116870321623</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5589087375410903</v>
+        <v>0.5475024367749456</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.154883083361443</v>
+        <v>0.156433083361443</v>
       </c>
       <c r="C51">
-        <v>-96.64621975351997</v>
+        <v>-133.4295008617623</v>
       </c>
       <c r="D51">
-        <v>872.9507802464801</v>
+        <v>860.7204991382379</v>
       </c>
       <c r="E51">
-        <v>299.797</v>
+        <v>324.3500000000001</v>
       </c>
       <c r="F51">
-        <v>1203.097</v>
+        <v>1227.65</v>
       </c>
       <c r="G51">
         <v>233.5</v>
@@ -5594,37 +5594,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M51">
-        <v>241.5818776</v>
+        <v>246.51212</v>
       </c>
       <c r="N51">
-        <v>-109.3152109333334</v>
+        <v>-114.2454533333334</v>
       </c>
       <c r="O51">
-        <v>-20.76989007733334</v>
+        <v>-21.70663613333334</v>
       </c>
       <c r="P51">
-        <v>-88.54532085600002</v>
+        <v>-92.53881720000004</v>
       </c>
       <c r="Q51">
-        <v>-34.54532085600002</v>
+        <v>-38.53881720000004</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1308359935601636</v>
+        <v>0.1325367134313669</v>
       </c>
       <c r="T51">
-        <v>1.65750979189917</v>
+        <v>1.690659987737154</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1040254629872397</v>
+        <v>0.1019449537274949</v>
       </c>
       <c r="W51">
-        <v>0.1799116870321623</v>
+        <v>0.180329453291519</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5475024367749456</v>
+        <v>0.5365523880394466</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.156433083361443</v>
+        <v>0.157983083361443</v>
       </c>
       <c r="C52">
-        <v>-133.4295008617623</v>
+        <v>-169.8748177217462</v>
       </c>
       <c r="D52">
-        <v>860.7204991382379</v>
+        <v>848.828182278254</v>
       </c>
       <c r="E52">
-        <v>324.3500000000001</v>
+        <v>348.9030000000002</v>
       </c>
       <c r="F52">
-        <v>1227.65</v>
+        <v>1252.203</v>
       </c>
       <c r="G52">
         <v>233.5</v>
@@ -5676,37 +5676,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M52">
-        <v>246.51212</v>
+        <v>251.4423624</v>
       </c>
       <c r="N52">
-        <v>-114.2454533333334</v>
+        <v>-119.1756957333334</v>
       </c>
       <c r="O52">
-        <v>-21.70663613333334</v>
+        <v>-22.64338218933334</v>
       </c>
       <c r="P52">
-        <v>-92.53881720000004</v>
+        <v>-96.53231354400003</v>
       </c>
       <c r="Q52">
-        <v>-38.53881720000004</v>
+        <v>-42.53231354400003</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1325367134313669</v>
+        <v>0.1343068504401704</v>
       </c>
       <c r="T52">
-        <v>1.690659987737154</v>
+        <v>1.725163252793014</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1019449537274949</v>
+        <v>0.09994603306617143</v>
       </c>
       <c r="W52">
-        <v>0.180329453291519</v>
+        <v>0.1807308365603128</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5365523880394466</v>
+        <v>0.5260317529798497</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.157983083361443</v>
+        <v>0.159533083361443</v>
       </c>
       <c r="C53">
-        <v>-169.8748177217462</v>
+        <v>-205.9959880697713</v>
       </c>
       <c r="D53">
-        <v>848.828182278254</v>
+        <v>837.2600119302289</v>
       </c>
       <c r="E53">
-        <v>348.9030000000002</v>
+        <v>373.4560000000001</v>
       </c>
       <c r="F53">
-        <v>1252.203</v>
+        <v>1276.756</v>
       </c>
       <c r="G53">
         <v>233.5</v>
@@ -5758,37 +5758,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M53">
-        <v>251.4423624</v>
+        <v>256.3726048</v>
       </c>
       <c r="N53">
-        <v>-119.1756957333334</v>
+        <v>-124.1059381333334</v>
       </c>
       <c r="O53">
-        <v>-22.64338218933334</v>
+        <v>-23.58012824533334</v>
       </c>
       <c r="P53">
-        <v>-96.53231354400003</v>
+        <v>-100.525809888</v>
       </c>
       <c r="Q53">
-        <v>-42.53231354400003</v>
+        <v>-46.52580988800004</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1343068504401704</v>
+        <v>0.1361507431576739</v>
       </c>
       <c r="T53">
-        <v>1.725163252793014</v>
+        <v>1.761104153892868</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.09994603306617143</v>
+        <v>0.09802399396874506</v>
       </c>
       <c r="W53">
-        <v>0.1807308365603128</v>
+        <v>0.181116782011076</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5260317529798497</v>
+        <v>0.5159157577302371</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.159533083361443</v>
+        <v>0.161083083361443</v>
       </c>
       <c r="C54">
-        <v>-205.9959880697713</v>
+        <v>-241.8060865151958</v>
       </c>
       <c r="D54">
-        <v>837.2600119302289</v>
+        <v>826.0029134848044</v>
       </c>
       <c r="E54">
-        <v>373.4560000000001</v>
+        <v>398.0090000000002</v>
       </c>
       <c r="F54">
-        <v>1276.756</v>
+        <v>1301.309</v>
       </c>
       <c r="G54">
         <v>233.5</v>
@@ -5840,37 +5840,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M54">
-        <v>256.3726048</v>
+        <v>261.3028472</v>
       </c>
       <c r="N54">
-        <v>-124.1059381333334</v>
+        <v>-129.0361805333334</v>
       </c>
       <c r="O54">
-        <v>-23.58012824533334</v>
+        <v>-24.51687430133334</v>
       </c>
       <c r="P54">
-        <v>-100.525809888</v>
+        <v>-104.519306232</v>
       </c>
       <c r="Q54">
-        <v>-46.52580988800004</v>
+        <v>-50.51930623200003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1361507431576739</v>
+        <v>0.1380730993950712</v>
       </c>
       <c r="T54">
-        <v>1.761104153892868</v>
+        <v>1.798574455039526</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.09802399396874506</v>
+        <v>0.09617448464858006</v>
       </c>
       <c r="W54">
-        <v>0.181116782011076</v>
+        <v>0.1814881634825651</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5159157577302371</v>
+        <v>0.5061814981504213</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.161083083361443</v>
+        <v>0.1818788269534893</v>
       </c>
       <c r="C55">
-        <v>-241.8060865151958</v>
+        <v>-392.5899277097942</v>
       </c>
       <c r="D55">
-        <v>826.0029134848044</v>
+        <v>699.7720722902059</v>
       </c>
       <c r="E55">
-        <v>398.0090000000002</v>
+        <v>422.5620000000001</v>
       </c>
       <c r="F55">
-        <v>1301.309</v>
+        <v>1325.862</v>
       </c>
       <c r="G55">
         <v>233.5</v>
@@ -5922,45 +5922,45 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M55">
-        <v>261.3028472</v>
+        <v>312.6382596</v>
       </c>
       <c r="N55">
-        <v>-129.0361805333334</v>
+        <v>-180.3715929333334</v>
       </c>
       <c r="O55">
-        <v>-24.51687430133334</v>
+        <v>-34.27060265733334</v>
       </c>
       <c r="P55">
-        <v>-104.519306232</v>
+        <v>-146.100990276</v>
       </c>
       <c r="Q55">
-        <v>-50.51930623200003</v>
+        <v>-92.10099027600003</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1380730993950712</v>
+        <v>0.1408306528428907</v>
       </c>
       <c r="T55">
-        <v>1.798574455039526</v>
+        <v>1.85232430436906</v>
       </c>
       <c r="U55">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.09617448464858006</v>
+        <v>0.08038256961518303</v>
       </c>
       <c r="W55">
-        <v>0.1814881634825651</v>
+        <v>0.2168457900847399</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.5061814981504213</v>
+        <v>0.4230661558693843</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1818788269534893</v>
+        <v>0.1837788269534892</v>
       </c>
       <c r="C56">
-        <v>-392.5899277097942</v>
+        <v>-426.7789491683591</v>
       </c>
       <c r="D56">
-        <v>699.7720722902059</v>
+        <v>690.1360508316411</v>
       </c>
       <c r="E56">
-        <v>422.5620000000001</v>
+        <v>447.1150000000002</v>
       </c>
       <c r="F56">
-        <v>1325.862</v>
+        <v>1350.415</v>
       </c>
       <c r="G56">
         <v>233.5</v>
@@ -6004,37 +6004,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M56">
-        <v>312.6382596</v>
+        <v>318.4278570000001</v>
       </c>
       <c r="N56">
-        <v>-180.3715929333334</v>
+        <v>-186.1611903333334</v>
       </c>
       <c r="O56">
-        <v>-34.27060265733334</v>
+        <v>-35.37062616333335</v>
       </c>
       <c r="P56">
-        <v>-146.100990276</v>
+        <v>-150.7905641700001</v>
       </c>
       <c r="Q56">
-        <v>-92.10099027600003</v>
+        <v>-96.79056417000007</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1408306528428907</v>
+        <v>0.1429424451282883</v>
       </c>
       <c r="T56">
-        <v>1.85232430436906</v>
+        <v>1.893487066688373</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.08038256961518303</v>
+        <v>0.07892106834945241</v>
       </c>
       <c r="W56">
-        <v>0.2168457900847399</v>
+        <v>0.2171904120831991</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4230661558693843</v>
+        <v>0.4153740439444864</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1837788269534892</v>
+        <v>0.1856788269534893</v>
       </c>
       <c r="C57">
-        <v>-426.7789491683591</v>
+        <v>-460.7061949004606</v>
       </c>
       <c r="D57">
-        <v>690.1360508316411</v>
+        <v>680.7618050995397</v>
       </c>
       <c r="E57">
-        <v>447.1150000000002</v>
+        <v>471.6680000000003</v>
       </c>
       <c r="F57">
-        <v>1350.415</v>
+        <v>1374.968</v>
       </c>
       <c r="G57">
         <v>233.5</v>
@@ -6086,37 +6086,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M57">
-        <v>318.4278570000001</v>
+        <v>324.2174544000001</v>
       </c>
       <c r="N57">
-        <v>-186.1611903333334</v>
+        <v>-191.9507877333334</v>
       </c>
       <c r="O57">
-        <v>-35.37062616333335</v>
+        <v>-36.47064966933335</v>
       </c>
       <c r="P57">
-        <v>-150.7905641700001</v>
+        <v>-155.4801380640001</v>
       </c>
       <c r="Q57">
-        <v>-96.79056417000007</v>
+        <v>-101.4801380640001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1429424451282883</v>
+        <v>0.145150227972113</v>
       </c>
       <c r="T57">
-        <v>1.893487066688373</v>
+        <v>1.936520863658563</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07892106834945241</v>
+        <v>0.07751176355749791</v>
       </c>
       <c r="W57">
-        <v>0.2171904120831991</v>
+        <v>0.217522726153142</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4153740439444864</v>
+        <v>0.4079566503026205</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1856788269534893</v>
+        <v>0.1875788269534893</v>
       </c>
       <c r="C58">
-        <v>-460.7061949004606</v>
+        <v>-494.3821891971578</v>
       </c>
       <c r="D58">
-        <v>680.7618050995397</v>
+        <v>671.6388108028424</v>
       </c>
       <c r="E58">
-        <v>471.6680000000003</v>
+        <v>496.2210000000002</v>
       </c>
       <c r="F58">
-        <v>1374.968</v>
+        <v>1399.521</v>
       </c>
       <c r="G58">
         <v>233.5</v>
@@ -6168,37 +6168,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M58">
-        <v>324.2174544000001</v>
+        <v>330.0070518000001</v>
       </c>
       <c r="N58">
-        <v>-191.9507877333334</v>
+        <v>-197.7403851333334</v>
       </c>
       <c r="O58">
-        <v>-36.47064966933335</v>
+        <v>-37.57067317533335</v>
       </c>
       <c r="P58">
-        <v>-155.4801380640001</v>
+        <v>-160.1697119580001</v>
       </c>
       <c r="Q58">
-        <v>-101.4801380640001</v>
+        <v>-106.1697119580001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.145150227972113</v>
+        <v>0.1474606983900691</v>
       </c>
       <c r="T58">
-        <v>1.936520863658563</v>
+        <v>1.981556232580855</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07751176355749791</v>
+        <v>0.07615190805648916</v>
       </c>
       <c r="W58">
-        <v>0.217522726153142</v>
+        <v>0.2178433800802799</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4079566503026205</v>
+        <v>0.4007995160867851</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1875788269534893</v>
+        <v>0.1894788269534892</v>
       </c>
       <c r="C59">
-        <v>-494.3821891971578</v>
+        <v>-527.8168996591908</v>
       </c>
       <c r="D59">
-        <v>671.6388108028424</v>
+        <v>662.7571003408095</v>
       </c>
       <c r="E59">
-        <v>496.2210000000002</v>
+        <v>520.7740000000003</v>
       </c>
       <c r="F59">
-        <v>1399.521</v>
+        <v>1424.074</v>
       </c>
       <c r="G59">
         <v>233.5</v>
@@ -6250,37 +6250,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M59">
-        <v>330.0070518000001</v>
+        <v>335.7966492000001</v>
       </c>
       <c r="N59">
-        <v>-197.7403851333334</v>
+        <v>-203.5299825333335</v>
       </c>
       <c r="O59">
-        <v>-37.57067317533335</v>
+        <v>-38.67069668133335</v>
       </c>
       <c r="P59">
-        <v>-160.1697119580001</v>
+        <v>-164.8592858520001</v>
       </c>
       <c r="Q59">
-        <v>-106.1697119580001</v>
+        <v>-110.8592858520001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1474606983900691</v>
+        <v>0.1498811912088803</v>
       </c>
       <c r="T59">
-        <v>1.981556232580855</v>
+        <v>2.028736142880399</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07615190805648916</v>
+        <v>0.07483894412448074</v>
       </c>
       <c r="W59">
-        <v>0.2178433800802799</v>
+        <v>0.2181529769754474</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4007995160867851</v>
+        <v>0.3938891796025301</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1894788269534892</v>
+        <v>0.1913788269534893</v>
       </c>
       <c r="C60">
-        <v>-527.8168996591903</v>
+        <v>-561.0197735247757</v>
       </c>
       <c r="D60">
-        <v>662.7571003408098</v>
+        <v>654.1072264752243</v>
       </c>
       <c r="E60">
-        <v>520.7740000000001</v>
+        <v>545.327</v>
       </c>
       <c r="F60">
-        <v>1424.074</v>
+        <v>1448.627</v>
       </c>
       <c r="G60">
         <v>233.5</v>
@@ -6332,37 +6332,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M60">
-        <v>335.7966492</v>
+        <v>341.5862466</v>
       </c>
       <c r="N60">
-        <v>-203.5299825333334</v>
+        <v>-209.3195799333333</v>
       </c>
       <c r="O60">
-        <v>-38.67069668133335</v>
+        <v>-39.77072018733333</v>
       </c>
       <c r="P60">
-        <v>-164.8592858520001</v>
+        <v>-169.548859746</v>
       </c>
       <c r="Q60">
-        <v>-110.8592858520001</v>
+        <v>-115.548859746</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1498811912088803</v>
+        <v>0.1524197568481213</v>
       </c>
       <c r="T60">
-        <v>2.028736142880399</v>
+        <v>2.078217512218945</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07483894412448075</v>
+        <v>0.07357048744440481</v>
       </c>
       <c r="W60">
-        <v>0.2181529769754474</v>
+        <v>0.2184520790606094</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3938891796025302</v>
+        <v>0.3872130918126568</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1913788269534893</v>
+        <v>0.1932788269534892</v>
       </c>
       <c r="C61">
-        <v>-561.0197735247757</v>
+        <v>-593.9997711892939</v>
       </c>
       <c r="D61">
-        <v>654.1072264752243</v>
+        <v>645.6802288107061</v>
       </c>
       <c r="E61">
-        <v>545.327</v>
+        <v>569.8800000000001</v>
       </c>
       <c r="F61">
-        <v>1448.627</v>
+        <v>1473.18</v>
       </c>
       <c r="G61">
         <v>233.5</v>
@@ -6414,37 +6414,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M61">
-        <v>341.5862466</v>
+        <v>347.375844</v>
       </c>
       <c r="N61">
-        <v>-209.3195799333333</v>
+        <v>-215.1091773333334</v>
       </c>
       <c r="O61">
-        <v>-39.77072018733333</v>
+        <v>-40.87074369333335</v>
       </c>
       <c r="P61">
-        <v>-169.548859746</v>
+        <v>-174.23843364</v>
       </c>
       <c r="Q61">
-        <v>-115.548859746</v>
+        <v>-120.23843364</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1524197568481213</v>
+        <v>0.1550852507693243</v>
       </c>
       <c r="T61">
-        <v>2.078217512218945</v>
+        <v>2.130172950024419</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07357048744440481</v>
+        <v>0.07234431265366473</v>
       </c>
       <c r="W61">
-        <v>0.2184520790606094</v>
+        <v>0.2187412110762659</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3872130918126568</v>
+        <v>0.3807595402824459</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1932788269534892</v>
+        <v>0.1951788269534892</v>
       </c>
       <c r="C62">
-        <v>-593.9997711892939</v>
+        <v>-626.7653971668851</v>
       </c>
       <c r="D62">
-        <v>645.6802288107061</v>
+        <v>637.4676028331151</v>
       </c>
       <c r="E62">
-        <v>569.8800000000001</v>
+        <v>594.4330000000002</v>
       </c>
       <c r="F62">
-        <v>1473.18</v>
+        <v>1497.733</v>
       </c>
       <c r="G62">
         <v>233.5</v>
@@ -6496,37 +6496,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M62">
-        <v>347.375844</v>
+        <v>353.1654414000001</v>
       </c>
       <c r="N62">
-        <v>-215.1091773333334</v>
+        <v>-220.8987747333334</v>
       </c>
       <c r="O62">
-        <v>-40.87074369333335</v>
+        <v>-41.97076719933335</v>
       </c>
       <c r="P62">
-        <v>-174.23843364</v>
+        <v>-178.9280075340001</v>
       </c>
       <c r="Q62">
-        <v>-120.23843364</v>
+        <v>-124.9280075340001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1550852507693243</v>
+        <v>0.1578874366864864</v>
       </c>
       <c r="T62">
-        <v>2.130172950024419</v>
+        <v>2.184792769255814</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07234431265366473</v>
+        <v>0.07115834031508003</v>
       </c>
       <c r="W62">
-        <v>0.2187412110762659</v>
+        <v>0.2190208633537041</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3807595402824459</v>
+        <v>0.3745175806056844</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1951788269534892</v>
+        <v>0.1970788269534892</v>
       </c>
       <c r="C63">
-        <v>-626.7653971668851</v>
+        <v>-659.3247287188564</v>
       </c>
       <c r="D63">
-        <v>637.4676028331151</v>
+        <v>629.4612712811437</v>
       </c>
       <c r="E63">
-        <v>594.4330000000002</v>
+        <v>618.9860000000001</v>
       </c>
       <c r="F63">
-        <v>1497.733</v>
+        <v>1522.286</v>
       </c>
       <c r="G63">
         <v>233.5</v>
@@ -6578,37 +6578,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M63">
-        <v>353.1654414000001</v>
+        <v>358.9550388</v>
       </c>
       <c r="N63">
-        <v>-220.8987747333334</v>
+        <v>-226.6883721333334</v>
       </c>
       <c r="O63">
-        <v>-41.97076719933335</v>
+        <v>-43.07079070533334</v>
       </c>
       <c r="P63">
-        <v>-178.9280075340001</v>
+        <v>-183.617581428</v>
       </c>
       <c r="Q63">
-        <v>-124.9280075340001</v>
+        <v>-129.617581428</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1578874366864864</v>
+        <v>0.1608371060729729</v>
       </c>
       <c r="T63">
-        <v>2.184792769255814</v>
+        <v>2.242287315815178</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07115834031508003</v>
+        <v>0.0700106251487078</v>
       </c>
       <c r="W63">
-        <v>0.2190208633537041</v>
+        <v>0.2192914945899347</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3745175806056844</v>
+        <v>0.3684769744668831</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1970788269534892</v>
+        <v>0.1989788269534892</v>
       </c>
       <c r="C64">
-        <v>-659.3247287188564</v>
+        <v>-691.6854423514809</v>
       </c>
       <c r="D64">
-        <v>629.4612712811437</v>
+        <v>621.6535576485193</v>
       </c>
       <c r="E64">
-        <v>618.9860000000001</v>
+        <v>643.5390000000002</v>
       </c>
       <c r="F64">
-        <v>1522.286</v>
+        <v>1546.839</v>
       </c>
       <c r="G64">
         <v>233.5</v>
@@ -6660,37 +6660,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M64">
-        <v>358.9550388</v>
+        <v>364.7446362000001</v>
       </c>
       <c r="N64">
-        <v>-226.6883721333334</v>
+        <v>-232.4779695333334</v>
       </c>
       <c r="O64">
-        <v>-43.07079070533334</v>
+        <v>-44.17081421133335</v>
       </c>
       <c r="P64">
-        <v>-183.617581428</v>
+        <v>-188.3071553220001</v>
       </c>
       <c r="Q64">
-        <v>-129.617581428</v>
+        <v>-134.3071553220001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1608371060729729</v>
+        <v>0.1639462170479181</v>
       </c>
       <c r="T64">
-        <v>2.242287315815178</v>
+        <v>2.302889675702075</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0700106251487078</v>
+        <v>0.06889934538444258</v>
       </c>
       <c r="W64">
-        <v>0.2192914945899347</v>
+        <v>0.2195535343583485</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3684769744668831</v>
+        <v>0.3626281336023294</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1989788269534892</v>
+        <v>0.2008788269534892</v>
       </c>
       <c r="C65">
-        <v>-691.6854423514809</v>
+        <v>-723.8548383659182</v>
       </c>
       <c r="D65">
-        <v>621.6535576485193</v>
+        <v>614.0371616340818</v>
       </c>
       <c r="E65">
-        <v>643.5390000000002</v>
+        <v>668.0920000000001</v>
       </c>
       <c r="F65">
-        <v>1546.839</v>
+        <v>1571.392</v>
       </c>
       <c r="G65">
         <v>233.5</v>
@@ -6742,37 +6742,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M65">
-        <v>364.7446362000001</v>
+        <v>370.5342336000001</v>
       </c>
       <c r="N65">
-        <v>-232.4779695333334</v>
+        <v>-238.2675669333334</v>
       </c>
       <c r="O65">
-        <v>-44.17081421133335</v>
+        <v>-45.27083771733334</v>
       </c>
       <c r="P65">
-        <v>-188.3071553220001</v>
+        <v>-192.9967292160001</v>
       </c>
       <c r="Q65">
-        <v>-134.3071553220001</v>
+        <v>-138.9967292160001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1639462170479181</v>
+        <v>0.1672280564103603</v>
       </c>
       <c r="T65">
-        <v>2.302889675702075</v>
+        <v>2.366858833360466</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06889934538444258</v>
+        <v>0.06782279311281067</v>
       </c>
       <c r="W65">
-        <v>0.2195535343583485</v>
+        <v>0.2198073853839992</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3626281336023294</v>
+        <v>0.356962069014793</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2008788269534892</v>
+        <v>0.2027788269534893</v>
       </c>
       <c r="C66">
-        <v>-723.8548383659182</v>
+        <v>-755.8398636252892</v>
       </c>
       <c r="D66">
-        <v>614.0371616340818</v>
+        <v>606.6051363747109</v>
       </c>
       <c r="E66">
-        <v>668.0920000000001</v>
+        <v>692.6450000000002</v>
       </c>
       <c r="F66">
-        <v>1571.392</v>
+        <v>1595.945</v>
       </c>
       <c r="G66">
         <v>233.5</v>
@@ -6824,37 +6824,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M66">
-        <v>370.5342336000001</v>
+        <v>376.323831</v>
       </c>
       <c r="N66">
-        <v>-238.2675669333334</v>
+        <v>-244.0571643333334</v>
       </c>
       <c r="O66">
-        <v>-45.27083771733334</v>
+        <v>-46.37086122333334</v>
       </c>
       <c r="P66">
-        <v>-192.9967292160001</v>
+        <v>-197.68630311</v>
       </c>
       <c r="Q66">
-        <v>-138.9967292160001</v>
+        <v>-143.68630311</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1672280564103603</v>
+        <v>0.1706974294506564</v>
       </c>
       <c r="T66">
-        <v>2.366858833360466</v>
+        <v>2.43448337145648</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06782279311281067</v>
+        <v>0.06677936552645974</v>
       </c>
       <c r="W66">
-        <v>0.2198073853839992</v>
+        <v>0.2200534256088608</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.356962069014793</v>
+        <v>0.3514703448761038</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2027788269534893</v>
+        <v>0.2046788269534892</v>
       </c>
       <c r="C67">
-        <v>-755.8398636252892</v>
+        <v>-787.647132688148</v>
       </c>
       <c r="D67">
-        <v>606.6051363747109</v>
+        <v>599.3508673118523</v>
       </c>
       <c r="E67">
-        <v>692.6450000000002</v>
+        <v>717.1980000000003</v>
       </c>
       <c r="F67">
-        <v>1595.945</v>
+        <v>1620.498</v>
       </c>
       <c r="G67">
         <v>233.5</v>
@@ -6906,37 +6906,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M67">
-        <v>376.323831</v>
+        <v>382.1134284000001</v>
       </c>
       <c r="N67">
-        <v>-244.0571643333334</v>
+        <v>-249.8467617333334</v>
       </c>
       <c r="O67">
-        <v>-46.37086122333334</v>
+        <v>-47.47088472933336</v>
       </c>
       <c r="P67">
-        <v>-197.68630311</v>
+        <v>-202.3758770040001</v>
       </c>
       <c r="Q67">
-        <v>-143.68630311</v>
+        <v>-148.3758770040001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1706974294506564</v>
+        <v>0.1743708832580286</v>
       </c>
       <c r="T67">
-        <v>2.43448337145648</v>
+        <v>2.50608582355814</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06677936552645974</v>
+        <v>0.065767556957877</v>
       </c>
       <c r="W67">
-        <v>0.2200534256088608</v>
+        <v>0.2202920100693326</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3514703448761038</v>
+        <v>0.3461450366204053</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2046788269534892</v>
+        <v>0.2065788269534893</v>
       </c>
       <c r="C68">
-        <v>-787.647132688148</v>
+        <v>-819.2829474434885</v>
       </c>
       <c r="D68">
-        <v>599.3508673118523</v>
+        <v>592.2680525565116</v>
       </c>
       <c r="E68">
-        <v>717.1980000000003</v>
+        <v>741.7510000000002</v>
       </c>
       <c r="F68">
-        <v>1620.498</v>
+        <v>1645.051</v>
       </c>
       <c r="G68">
         <v>233.5</v>
@@ -6988,37 +6988,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M68">
-        <v>382.1134284000001</v>
+        <v>387.9030258000001</v>
       </c>
       <c r="N68">
-        <v>-249.8467617333334</v>
+        <v>-255.6363591333334</v>
       </c>
       <c r="O68">
-        <v>-47.47088472933336</v>
+        <v>-48.57090823533335</v>
       </c>
       <c r="P68">
-        <v>-202.3758770040001</v>
+        <v>-207.0654508980001</v>
       </c>
       <c r="Q68">
-        <v>-148.3758770040001</v>
+        <v>-153.0654508980001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1743708832580286</v>
+        <v>0.178266970629484</v>
       </c>
       <c r="T68">
-        <v>2.50608582355814</v>
+        <v>2.582027818211417</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.065767556957877</v>
+        <v>0.0647859516301475</v>
       </c>
       <c r="W68">
-        <v>0.2202920100693326</v>
+        <v>0.2205234726056113</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3461450366204053</v>
+        <v>0.3409786927902501</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2065788269534893</v>
+        <v>0.2084788269534892</v>
       </c>
       <c r="C69">
-        <v>-819.2829474434885</v>
+        <v>-850.7533153697959</v>
       </c>
       <c r="D69">
-        <v>592.2680525565116</v>
+        <v>585.3506846302043</v>
       </c>
       <c r="E69">
-        <v>741.7510000000002</v>
+        <v>766.3040000000003</v>
       </c>
       <c r="F69">
-        <v>1645.051</v>
+        <v>1669.604</v>
       </c>
       <c r="G69">
         <v>233.5</v>
@@ -7070,37 +7070,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M69">
-        <v>387.9030258000001</v>
+        <v>393.6926232000001</v>
       </c>
       <c r="N69">
-        <v>-255.6363591333334</v>
+        <v>-261.4259565333334</v>
       </c>
       <c r="O69">
-        <v>-48.57090823533335</v>
+        <v>-49.67093174133335</v>
       </c>
       <c r="P69">
-        <v>-207.0654508980001</v>
+        <v>-211.7550247920001</v>
       </c>
       <c r="Q69">
-        <v>-153.0654508980001</v>
+        <v>-157.7550247920001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.178266970629484</v>
+        <v>0.1824065634616554</v>
       </c>
       <c r="T69">
-        <v>2.582027818211417</v>
+        <v>2.662716187530524</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0647859516301475</v>
+        <v>0.06383321704735122</v>
       </c>
       <c r="W69">
-        <v>0.2205234726056113</v>
+        <v>0.2207481274202346</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3409786927902501</v>
+        <v>0.335964300249217</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2084788269534892</v>
+        <v>0.2103788269534893</v>
       </c>
       <c r="C70">
-        <v>-850.7533153697959</v>
+        <v>-882.0639665293326</v>
       </c>
       <c r="D70">
-        <v>585.3506846302043</v>
+        <v>578.5930334706678</v>
       </c>
       <c r="E70">
-        <v>766.3040000000003</v>
+        <v>790.8570000000004</v>
       </c>
       <c r="F70">
-        <v>1669.604</v>
+        <v>1694.157</v>
       </c>
       <c r="G70">
         <v>233.5</v>
@@ -7152,37 +7152,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M70">
-        <v>393.6926232000001</v>
+        <v>399.4822206000001</v>
       </c>
       <c r="N70">
-        <v>-261.4259565333334</v>
+        <v>-267.2155539333335</v>
       </c>
       <c r="O70">
-        <v>-49.67093174133335</v>
+        <v>-50.77095524733336</v>
       </c>
       <c r="P70">
-        <v>-211.7550247920001</v>
+        <v>-216.4445986860001</v>
       </c>
       <c r="Q70">
-        <v>-157.7550247920001</v>
+        <v>-162.4445986860001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1824065634616554</v>
+        <v>0.1868132267991282</v>
       </c>
       <c r="T70">
-        <v>2.662716187530524</v>
+        <v>2.748610258096025</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06383321704735122</v>
+        <v>0.06290809795970843</v>
       </c>
       <c r="W70">
-        <v>0.2207481274202346</v>
+        <v>0.2209662705011008</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.335964300249217</v>
+        <v>0.3310952524195181</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2103788269534893</v>
+        <v>0.2122788269534892</v>
       </c>
       <c r="C71">
-        <v>-882.0639665293326</v>
+        <v>-913.2203693987036</v>
       </c>
       <c r="D71">
-        <v>578.5930334706678</v>
+        <v>571.9896306012967</v>
       </c>
       <c r="E71">
-        <v>790.8570000000004</v>
+        <v>815.4100000000003</v>
       </c>
       <c r="F71">
-        <v>1694.157</v>
+        <v>1718.71</v>
       </c>
       <c r="G71">
         <v>233.5</v>
@@ -7234,37 +7234,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M71">
-        <v>399.4822206000001</v>
+        <v>405.2718180000001</v>
       </c>
       <c r="N71">
-        <v>-267.2155539333335</v>
+        <v>-273.0051513333334</v>
       </c>
       <c r="O71">
-        <v>-50.77095524733336</v>
+        <v>-51.87097875333335</v>
       </c>
       <c r="P71">
-        <v>-216.4445986860001</v>
+        <v>-221.13417258</v>
       </c>
       <c r="Q71">
-        <v>-162.4445986860001</v>
+        <v>-167.13417258</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1868132267991282</v>
+        <v>0.1915136676924324</v>
       </c>
       <c r="T71">
-        <v>2.748610258096025</v>
+        <v>2.840230600032559</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06290809795970843</v>
+        <v>0.06200941084599833</v>
       </c>
       <c r="W71">
-        <v>0.2209662705011008</v>
+        <v>0.2211781809225136</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3310952524195181</v>
+        <v>0.3263653202420964</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2122788269534892</v>
+        <v>0.2141788269534893</v>
       </c>
       <c r="C72">
-        <v>-913.2203693987036</v>
+        <v>-944.2277456276266</v>
       </c>
       <c r="D72">
-        <v>571.9896306012967</v>
+        <v>565.5352543723737</v>
       </c>
       <c r="E72">
-        <v>815.4100000000003</v>
+        <v>839.9630000000004</v>
       </c>
       <c r="F72">
-        <v>1718.71</v>
+        <v>1743.263</v>
       </c>
       <c r="G72">
         <v>233.5</v>
@@ -7316,37 +7316,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M72">
-        <v>405.2718180000001</v>
+        <v>411.0614154000001</v>
       </c>
       <c r="N72">
-        <v>-273.0051513333334</v>
+        <v>-278.7947487333334</v>
       </c>
       <c r="O72">
-        <v>-51.87097875333335</v>
+        <v>-52.97100225933335</v>
       </c>
       <c r="P72">
-        <v>-221.13417258</v>
+        <v>-225.8237464740001</v>
       </c>
       <c r="Q72">
-        <v>-167.13417258</v>
+        <v>-171.8237464740001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1915136676924324</v>
+        <v>0.196538276923206</v>
       </c>
       <c r="T72">
-        <v>2.840230600032559</v>
+        <v>2.938169586240579</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06200941084599833</v>
+        <v>0.06113603886225186</v>
       </c>
       <c r="W72">
-        <v>0.2211781809225136</v>
+        <v>0.221384122036281</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3263653202420964</v>
+        <v>0.3217686255907993</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2141788269534892</v>
+        <v>0.2160788269534892</v>
       </c>
       <c r="C73">
-        <v>-944.2277456276259</v>
+        <v>-975.0910838096071</v>
       </c>
       <c r="D73">
-        <v>565.5352543723742</v>
+        <v>559.2249161903929</v>
       </c>
       <c r="E73">
-        <v>839.9630000000002</v>
+        <v>864.5160000000001</v>
       </c>
       <c r="F73">
-        <v>1743.263</v>
+        <v>1767.816</v>
       </c>
       <c r="G73">
         <v>233.5</v>
@@ -7398,37 +7398,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M73">
-        <v>411.0614154</v>
+        <v>416.8510128</v>
       </c>
       <c r="N73">
-        <v>-278.7947487333334</v>
+        <v>-284.5843461333334</v>
       </c>
       <c r="O73">
-        <v>-52.97100225933335</v>
+        <v>-54.07102576533335</v>
       </c>
       <c r="P73">
-        <v>-225.823746474</v>
+        <v>-230.5133203680001</v>
       </c>
       <c r="Q73">
-        <v>-171.823746474</v>
+        <v>-176.5133203680001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1965382769232059</v>
+        <v>0.2019217868133204</v>
       </c>
       <c r="T73">
-        <v>2.938169586240578</v>
+        <v>3.043104214320598</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06113603886225187</v>
+        <v>0.06028692721138727</v>
       </c>
       <c r="W73">
-        <v>0.221384122036281</v>
+        <v>0.2215843425635549</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3217686255907993</v>
+        <v>0.3172996169020382</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2160788269534892</v>
+        <v>0.2179788269534892</v>
       </c>
       <c r="C74">
-        <v>-975.0910838096071</v>
+        <v>-1005.815152340866</v>
       </c>
       <c r="D74">
-        <v>559.2249161903929</v>
+        <v>553.0538476591342</v>
       </c>
       <c r="E74">
-        <v>864.5160000000001</v>
+        <v>889.0690000000002</v>
       </c>
       <c r="F74">
-        <v>1767.816</v>
+        <v>1792.369</v>
       </c>
       <c r="G74">
         <v>233.5</v>
@@ -7480,37 +7480,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M74">
-        <v>416.8510128</v>
+        <v>422.6406102</v>
       </c>
       <c r="N74">
-        <v>-284.5843461333334</v>
+        <v>-290.3739435333334</v>
       </c>
       <c r="O74">
-        <v>-54.07102576533335</v>
+        <v>-55.17104927133335</v>
       </c>
       <c r="P74">
-        <v>-230.5133203680001</v>
+        <v>-235.202894262</v>
       </c>
       <c r="Q74">
-        <v>-176.5133203680001</v>
+        <v>-181.202894262</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2019217868133204</v>
+        <v>0.2077040752138138</v>
       </c>
       <c r="T74">
-        <v>3.043104214320598</v>
+        <v>3.155811777813954</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06028692721138727</v>
+        <v>0.05946107889342305</v>
       </c>
       <c r="W74">
-        <v>0.2215843425635549</v>
+        <v>0.2217790775969309</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3172996169020382</v>
+        <v>0.3129530468074898</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2179788269534892</v>
+        <v>0.2198788269534892</v>
       </c>
       <c r="C75">
-        <v>-1005.815152340866</v>
+        <v>-1036.404511437157</v>
       </c>
       <c r="D75">
-        <v>553.0538476591342</v>
+        <v>547.0174885628435</v>
       </c>
       <c r="E75">
-        <v>889.0690000000002</v>
+        <v>913.6220000000001</v>
       </c>
       <c r="F75">
-        <v>1792.369</v>
+        <v>1816.922</v>
       </c>
       <c r="G75">
         <v>233.5</v>
@@ -7562,37 +7562,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M75">
-        <v>422.6406102</v>
+        <v>428.4302076</v>
       </c>
       <c r="N75">
-        <v>-290.3739435333334</v>
+        <v>-296.1635409333334</v>
       </c>
       <c r="O75">
-        <v>-55.17104927133335</v>
+        <v>-56.27107277733334</v>
       </c>
       <c r="P75">
-        <v>-235.202894262</v>
+        <v>-239.892468156</v>
       </c>
       <c r="Q75">
-        <v>-181.202894262</v>
+        <v>-185.892468156</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2077040752138138</v>
+        <v>0.2139311550297297</v>
       </c>
       <c r="T75">
-        <v>3.155811777813954</v>
+        <v>3.277189153883721</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05946107889342305</v>
+        <v>0.05865755080026869</v>
       </c>
       <c r="W75">
-        <v>0.2217790775969309</v>
+        <v>0.2219685495212967</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3129530468074898</v>
+        <v>0.3087239515803616</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2198788269534892</v>
+        <v>0.2217788269534892</v>
       </c>
       <c r="C76">
-        <v>-1036.404511437157</v>
+        <v>-1066.863524372134</v>
       </c>
       <c r="D76">
-        <v>547.0174885628435</v>
+        <v>541.1114756278665</v>
       </c>
       <c r="E76">
-        <v>913.6220000000001</v>
+        <v>938.1750000000002</v>
       </c>
       <c r="F76">
-        <v>1816.922</v>
+        <v>1841.475</v>
       </c>
       <c r="G76">
         <v>233.5</v>
@@ -7644,37 +7644,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M76">
-        <v>428.4302076</v>
+        <v>434.2198050000001</v>
       </c>
       <c r="N76">
-        <v>-296.1635409333334</v>
+        <v>-301.9531383333334</v>
       </c>
       <c r="O76">
-        <v>-56.27107277733334</v>
+        <v>-57.37109628333335</v>
       </c>
       <c r="P76">
-        <v>-239.892468156</v>
+        <v>-244.5820420500001</v>
       </c>
       <c r="Q76">
-        <v>-185.892468156</v>
+        <v>-190.5820420500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2139311550297297</v>
+        <v>0.2206564012309189</v>
       </c>
       <c r="T76">
-        <v>3.277189153883721</v>
+        <v>3.40827672003907</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05865755080026869</v>
+        <v>0.05787545012293178</v>
       </c>
       <c r="W76">
-        <v>0.2219685495212967</v>
+        <v>0.2221529688610127</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3087239515803616</v>
+        <v>0.3046076322259567</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2217788269534892</v>
+        <v>0.2236788269534893</v>
       </c>
       <c r="C77">
-        <v>-1066.863524372134</v>
+        <v>-1097.196367995467</v>
       </c>
       <c r="D77">
-        <v>541.1114756278665</v>
+        <v>535.3316320045336</v>
       </c>
       <c r="E77">
-        <v>938.1750000000002</v>
+        <v>962.7280000000003</v>
       </c>
       <c r="F77">
-        <v>1841.475</v>
+        <v>1866.028</v>
       </c>
       <c r="G77">
         <v>233.5</v>
@@ -7726,37 +7726,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M77">
-        <v>434.2198050000001</v>
+        <v>440.0094024000001</v>
       </c>
       <c r="N77">
-        <v>-301.9531383333334</v>
+        <v>-307.7427357333334</v>
       </c>
       <c r="O77">
-        <v>-57.37109628333335</v>
+        <v>-58.47111978933335</v>
       </c>
       <c r="P77">
-        <v>-244.5820420500001</v>
+        <v>-249.271615944</v>
       </c>
       <c r="Q77">
-        <v>-190.5820420500001</v>
+        <v>-195.271615944</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2206564012309189</v>
+        <v>0.2279420846155405</v>
       </c>
       <c r="T77">
-        <v>3.40827672003907</v>
+        <v>3.550288250040699</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05787545012293178</v>
+        <v>0.05711393104236688</v>
       </c>
       <c r="W77">
-        <v>0.2221529688610127</v>
+        <v>0.2223325350602099</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3046076322259567</v>
+        <v>0.3005996370650889</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2236788269534893</v>
+        <v>0.2255788269534892</v>
       </c>
       <c r="C78">
-        <v>-1097.196367995467</v>
+        <v>-1127.407042583986</v>
       </c>
       <c r="D78">
-        <v>535.3316320045336</v>
+        <v>529.6739574160143</v>
       </c>
       <c r="E78">
-        <v>962.7280000000003</v>
+        <v>987.2810000000002</v>
       </c>
       <c r="F78">
-        <v>1866.028</v>
+        <v>1890.581</v>
       </c>
       <c r="G78">
         <v>233.5</v>
@@ -7808,37 +7808,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M78">
-        <v>440.0094024000001</v>
+        <v>445.7989998</v>
       </c>
       <c r="N78">
-        <v>-307.7427357333334</v>
+        <v>-313.5323331333334</v>
       </c>
       <c r="O78">
-        <v>-58.47111978933335</v>
+        <v>-59.57114329533334</v>
       </c>
       <c r="P78">
-        <v>-249.271615944</v>
+        <v>-253.9611898380001</v>
       </c>
       <c r="Q78">
-        <v>-195.271615944</v>
+        <v>-199.9611898380001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2279420846155405</v>
+        <v>0.2358613056857814</v>
       </c>
       <c r="T78">
-        <v>3.550288250040699</v>
+        <v>3.70464860873812</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05711393104236688</v>
+        <v>0.0563721916781803</v>
       </c>
       <c r="W78">
-        <v>0.2223325350602099</v>
+        <v>0.2225074372022851</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3005996370650889</v>
+        <v>0.2966957456746332</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2255788269534892</v>
+        <v>0.2274788269534893</v>
       </c>
       <c r="C79">
-        <v>-1127.407042583986</v>
+        <v>-1157.499381074696</v>
       </c>
       <c r="D79">
-        <v>529.6739574160143</v>
+        <v>524.1346189253045</v>
       </c>
       <c r="E79">
-        <v>987.2810000000002</v>
+        <v>1011.834</v>
       </c>
       <c r="F79">
-        <v>1890.581</v>
+        <v>1915.134</v>
       </c>
       <c r="G79">
         <v>233.5</v>
@@ -7890,37 +7890,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M79">
-        <v>445.7989998</v>
+        <v>451.5885972000001</v>
       </c>
       <c r="N79">
-        <v>-313.5323331333334</v>
+        <v>-319.3219305333334</v>
       </c>
       <c r="O79">
-        <v>-59.57114329533334</v>
+        <v>-60.67116680133336</v>
       </c>
       <c r="P79">
-        <v>-253.9611898380001</v>
+        <v>-258.6507637320001</v>
       </c>
       <c r="Q79">
-        <v>-199.9611898380001</v>
+        <v>-204.6507637320001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2358613056857814</v>
+        <v>0.244500455944226</v>
       </c>
       <c r="T79">
-        <v>3.70464860873812</v>
+        <v>3.873041727317126</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0563721916781803</v>
+        <v>0.05564947127204978</v>
       </c>
       <c r="W79">
-        <v>0.2225074372022851</v>
+        <v>0.2226778546740507</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2966957456746332</v>
+        <v>0.2928919540634198</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2274788269534893</v>
+        <v>0.2293788269534893</v>
       </c>
       <c r="C80">
-        <v>-1157.499381074696</v>
+        <v>-1187.477057724418</v>
       </c>
       <c r="D80">
-        <v>524.1346189253045</v>
+        <v>518.7099422755819</v>
       </c>
       <c r="E80">
-        <v>1011.834</v>
+        <v>1036.387</v>
       </c>
       <c r="F80">
-        <v>1915.134</v>
+        <v>1939.687</v>
       </c>
       <c r="G80">
         <v>233.5</v>
@@ -7972,37 +7972,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M80">
-        <v>451.5885972000001</v>
+        <v>457.3781946</v>
       </c>
       <c r="N80">
-        <v>-319.3219305333334</v>
+        <v>-325.1115279333334</v>
       </c>
       <c r="O80">
-        <v>-60.67116680133336</v>
+        <v>-61.77119030733334</v>
       </c>
       <c r="P80">
-        <v>-258.6507637320001</v>
+        <v>-263.3403376260001</v>
       </c>
       <c r="Q80">
-        <v>-204.6507637320001</v>
+        <v>-209.3403376260001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.244500455944226</v>
+        <v>0.2539623824177606</v>
       </c>
       <c r="T80">
-        <v>3.873041727317126</v>
+        <v>4.057472285760799</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05564947127204978</v>
+        <v>0.05494504758506182</v>
       </c>
       <c r="W80">
-        <v>0.2226778546740507</v>
+        <v>0.2228439577794424</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2928919540634198</v>
+        <v>0.2891844609740095</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2293788269534893</v>
+        <v>0.2312788269534893</v>
       </c>
       <c r="C81">
-        <v>-1187.477057724418</v>
+        <v>-1217.343596237203</v>
       </c>
       <c r="D81">
-        <v>518.7099422755819</v>
+        <v>513.3964037627969</v>
       </c>
       <c r="E81">
-        <v>1036.387</v>
+        <v>1060.94</v>
       </c>
       <c r="F81">
-        <v>1939.687</v>
+        <v>1964.24</v>
       </c>
       <c r="G81">
         <v>233.5</v>
@@ -8054,37 +8054,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M81">
-        <v>457.3781946</v>
+        <v>463.1677920000001</v>
       </c>
       <c r="N81">
-        <v>-325.1115279333334</v>
+        <v>-330.9011253333334</v>
       </c>
       <c r="O81">
-        <v>-61.77119030733334</v>
+        <v>-62.87121381333335</v>
       </c>
       <c r="P81">
-        <v>-263.3403376260001</v>
+        <v>-268.0299115200001</v>
       </c>
       <c r="Q81">
-        <v>-209.3403376260001</v>
+        <v>-214.0299115200001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2539623824177606</v>
+        <v>0.2643705015386486</v>
       </c>
       <c r="T81">
-        <v>4.057472285760799</v>
+        <v>4.260345900048838</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05494504758506182</v>
+        <v>0.05425823449024854</v>
       </c>
       <c r="W81">
-        <v>0.2228439577794424</v>
+        <v>0.2230059083071994</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2891844609740095</v>
+        <v>0.2855696552118344</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2312788269534893</v>
+        <v>0.2331788269534892</v>
       </c>
       <c r="C82">
-        <v>-1217.343596237203</v>
+        <v>-1247.102377397267</v>
       </c>
       <c r="D82">
-        <v>513.3964037627969</v>
+        <v>508.190622602733</v>
       </c>
       <c r="E82">
-        <v>1060.94</v>
+        <v>1085.493</v>
       </c>
       <c r="F82">
-        <v>1964.24</v>
+        <v>1988.793</v>
       </c>
       <c r="G82">
         <v>233.5</v>
@@ -8136,37 +8136,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M82">
-        <v>463.1677920000001</v>
+        <v>468.9573894000001</v>
       </c>
       <c r="N82">
-        <v>-330.9011253333334</v>
+        <v>-336.6907227333335</v>
       </c>
       <c r="O82">
-        <v>-62.87121381333335</v>
+        <v>-63.97123731933336</v>
       </c>
       <c r="P82">
-        <v>-268.0299115200001</v>
+        <v>-272.7194854140001</v>
       </c>
       <c r="Q82">
-        <v>-214.0299115200001</v>
+        <v>-218.7194854140001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2643705015386486</v>
+        <v>0.2758742121459459</v>
       </c>
       <c r="T82">
-        <v>4.260345900048838</v>
+        <v>4.484574631630357</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05425823449024854</v>
+        <v>0.05358837974345534</v>
       </c>
       <c r="W82">
-        <v>0.2230059083071994</v>
+        <v>0.2231638600564932</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2855696552118344</v>
+        <v>0.2820441039129228</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2331788269534892</v>
+        <v>0.2350788269534893</v>
       </c>
       <c r="C83">
-        <v>-1247.102377397267</v>
+        <v>-1276.75664624221</v>
       </c>
       <c r="D83">
-        <v>508.190622602733</v>
+        <v>503.0893537577899</v>
       </c>
       <c r="E83">
-        <v>1085.493</v>
+        <v>1110.046</v>
       </c>
       <c r="F83">
-        <v>1988.793</v>
+        <v>2013.346</v>
       </c>
       <c r="G83">
         <v>233.5</v>
@@ -8218,37 +8218,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M83">
-        <v>468.9573894000001</v>
+        <v>474.7469868000001</v>
       </c>
       <c r="N83">
-        <v>-336.6907227333335</v>
+        <v>-342.4803201333334</v>
       </c>
       <c r="O83">
-        <v>-63.97123731933336</v>
+        <v>-65.07126082533335</v>
       </c>
       <c r="P83">
-        <v>-272.7194854140001</v>
+        <v>-277.4090593080001</v>
       </c>
       <c r="Q83">
-        <v>-218.7194854140001</v>
+        <v>-223.4090593080001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2758742121459459</v>
+        <v>0.2886561128207207</v>
       </c>
       <c r="T83">
-        <v>4.484574631630357</v>
+        <v>4.733717666720933</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05358837974345534</v>
+        <v>0.05293486291731565</v>
       </c>
       <c r="W83">
-        <v>0.2231638600564932</v>
+        <v>0.223317959324097</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2820441039129228</v>
+        <v>0.2786045416700823</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2350788269534893</v>
+        <v>0.2369788269534893</v>
       </c>
       <c r="C84">
-        <v>-1276.75664624221</v>
+        <v>-1306.309518808498</v>
       </c>
       <c r="D84">
-        <v>503.0893537577899</v>
+        <v>498.0894811915022</v>
       </c>
       <c r="E84">
-        <v>1110.046</v>
+        <v>1134.599</v>
       </c>
       <c r="F84">
-        <v>2013.346</v>
+        <v>2037.899</v>
       </c>
       <c r="G84">
         <v>233.5</v>
@@ -8300,37 +8300,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M84">
-        <v>474.7469868000001</v>
+        <v>480.5365842000001</v>
       </c>
       <c r="N84">
-        <v>-342.4803201333334</v>
+        <v>-348.2699175333335</v>
       </c>
       <c r="O84">
-        <v>-65.07126082533335</v>
+        <v>-66.17128433133335</v>
       </c>
       <c r="P84">
-        <v>-277.4090593080001</v>
+        <v>-282.0986332020001</v>
       </c>
       <c r="Q84">
-        <v>-223.4090593080001</v>
+        <v>-228.0986332020001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2886561128207207</v>
+        <v>0.3029417665160573</v>
       </c>
       <c r="T84">
-        <v>4.733717666720933</v>
+        <v>5.012171647116282</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05293486291731565</v>
+        <v>0.0522970934845769</v>
       </c>
       <c r="W84">
-        <v>0.223317959324097</v>
+        <v>0.2234683453563368</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2786045416700823</v>
+        <v>0.2752478604451416</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2369788269534893</v>
+        <v>0.2388788269534892</v>
       </c>
       <c r="C85">
-        <v>-1306.309518808498</v>
+        <v>-1335.763988478664</v>
       </c>
       <c r="D85">
-        <v>498.0894811915022</v>
+        <v>493.1880115213362</v>
       </c>
       <c r="E85">
-        <v>1134.599</v>
+        <v>1159.152</v>
       </c>
       <c r="F85">
-        <v>2037.899</v>
+        <v>2062.452</v>
       </c>
       <c r="G85">
         <v>233.5</v>
@@ -8382,37 +8382,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M85">
-        <v>480.5365842000001</v>
+        <v>486.3261816000001</v>
       </c>
       <c r="N85">
-        <v>-348.2699175333335</v>
+        <v>-354.0595149333334</v>
       </c>
       <c r="O85">
-        <v>-66.17128433133335</v>
+        <v>-67.27130783733335</v>
       </c>
       <c r="P85">
-        <v>-282.0986332020001</v>
+        <v>-286.7882070960001</v>
       </c>
       <c r="Q85">
-        <v>-228.0986332020001</v>
+        <v>-232.7882070960001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3029417665160573</v>
+        <v>0.3190131269233109</v>
       </c>
       <c r="T85">
-        <v>5.012171647116282</v>
+        <v>5.325432375061051</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0522970934845769</v>
+        <v>0.05167450903833194</v>
       </c>
       <c r="W85">
-        <v>0.2234683453563368</v>
+        <v>0.2236151507687613</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2752478604451416</v>
+        <v>0.2719711002017471</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2388788269534892</v>
+        <v>0.2407788269534892</v>
       </c>
       <c r="C86">
-        <v>-1335.763988478664</v>
+        <v>-1365.12293195741</v>
       </c>
       <c r="D86">
-        <v>493.1880115213362</v>
+        <v>488.3820680425904</v>
       </c>
       <c r="E86">
-        <v>1159.152</v>
+        <v>1183.705</v>
       </c>
       <c r="F86">
-        <v>2062.452</v>
+        <v>2087.005</v>
       </c>
       <c r="G86">
         <v>233.5</v>
@@ -8464,37 +8464,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M86">
-        <v>486.3261816000001</v>
+        <v>492.115779</v>
       </c>
       <c r="N86">
-        <v>-354.0595149333334</v>
+        <v>-359.8491123333334</v>
       </c>
       <c r="O86">
-        <v>-67.27130783733335</v>
+        <v>-68.37133134333334</v>
       </c>
       <c r="P86">
-        <v>-286.7882070960001</v>
+        <v>-291.47778099</v>
       </c>
       <c r="Q86">
-        <v>-232.7882070960001</v>
+        <v>-237.47778099</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3190131269233107</v>
+        <v>0.3372273353848648</v>
       </c>
       <c r="T86">
-        <v>5.325432375061047</v>
+        <v>5.680461200065118</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05167450903833194</v>
+        <v>0.05106657363788099</v>
       </c>
       <c r="W86">
-        <v>0.2236151507687613</v>
+        <v>0.2237585019361877</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2719711002017471</v>
+        <v>0.2687714401993736</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2407788269534892</v>
+        <v>0.2426788269534892</v>
       </c>
       <c r="C87">
-        <v>-1365.12293195741</v>
+        <v>-1394.389114901658</v>
       </c>
       <c r="D87">
-        <v>488.3820680425904</v>
+        <v>483.6688850983418</v>
       </c>
       <c r="E87">
-        <v>1183.705</v>
+        <v>1208.258</v>
       </c>
       <c r="F87">
-        <v>2087.005</v>
+        <v>2111.558</v>
       </c>
       <c r="G87">
         <v>233.5</v>
@@ -8546,37 +8546,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M87">
-        <v>492.115779</v>
+        <v>497.9053764</v>
       </c>
       <c r="N87">
-        <v>-359.8491123333334</v>
+        <v>-365.6387097333334</v>
       </c>
       <c r="O87">
-        <v>-68.37133134333334</v>
+        <v>-69.47135484933334</v>
       </c>
       <c r="P87">
-        <v>-291.47778099</v>
+        <v>-296.167354884</v>
       </c>
       <c r="Q87">
-        <v>-237.47778099</v>
+        <v>-242.167354884</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3372273353848648</v>
+        <v>0.3580435736266408</v>
       </c>
       <c r="T87">
-        <v>5.680461200065118</v>
+        <v>6.086208428641196</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05106657363788099</v>
+        <v>0.05047277626999864</v>
       </c>
       <c r="W87">
-        <v>0.2237585019361877</v>
+        <v>0.2238985193555343</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2687714401993736</v>
+        <v>0.2656461908947297</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2426788269534892</v>
+        <v>0.2445788269534893</v>
       </c>
       <c r="C88">
-        <v>-1394.389114901658</v>
+        <v>-1423.565197227735</v>
       </c>
       <c r="D88">
-        <v>483.6688850983418</v>
+        <v>479.0458027722651</v>
       </c>
       <c r="E88">
-        <v>1208.258</v>
+        <v>1232.811</v>
       </c>
       <c r="F88">
-        <v>2111.558</v>
+        <v>2136.111</v>
       </c>
       <c r="G88">
         <v>233.5</v>
@@ -8628,37 +8628,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M88">
-        <v>497.9053764</v>
+        <v>503.6949738000001</v>
       </c>
       <c r="N88">
-        <v>-365.6387097333334</v>
+        <v>-371.4283071333334</v>
       </c>
       <c r="O88">
-        <v>-69.47135484933334</v>
+        <v>-70.57137835533335</v>
       </c>
       <c r="P88">
-        <v>-296.167354884</v>
+        <v>-300.8569287780001</v>
       </c>
       <c r="Q88">
-        <v>-242.167354884</v>
+        <v>-246.8569287780001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3580435736266408</v>
+        <v>0.3820623100594593</v>
       </c>
       <c r="T88">
-        <v>6.086208428641196</v>
+        <v>6.554378307767443</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05047277626999864</v>
+        <v>0.04989262941632049</v>
       </c>
       <c r="W88">
-        <v>0.2238985193555343</v>
+        <v>0.2240353179836317</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2656461908947297</v>
+        <v>0.2625927864016868</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2445788269534893</v>
+        <v>0.2464788269534893</v>
       </c>
       <c r="C89">
-        <v>-1423.565197227735</v>
+        <v>-1452.65373811705</v>
       </c>
       <c r="D89">
-        <v>479.0458027722651</v>
+        <v>474.5102618829503</v>
       </c>
       <c r="E89">
-        <v>1232.811</v>
+        <v>1257.364</v>
       </c>
       <c r="F89">
-        <v>2136.111</v>
+        <v>2160.664</v>
       </c>
       <c r="G89">
         <v>233.5</v>
@@ -8710,37 +8710,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M89">
-        <v>503.6949738000001</v>
+        <v>509.4845712000001</v>
       </c>
       <c r="N89">
-        <v>-371.4283071333334</v>
+        <v>-377.2179045333334</v>
       </c>
       <c r="O89">
-        <v>-70.57137835533335</v>
+        <v>-71.67140186133335</v>
       </c>
       <c r="P89">
-        <v>-300.8569287780001</v>
+        <v>-305.5465026720001</v>
       </c>
       <c r="Q89">
-        <v>-246.8569287780001</v>
+        <v>-251.5465026720001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3820623100594593</v>
+        <v>0.410084169231081</v>
       </c>
       <c r="T89">
-        <v>6.554378307767443</v>
+        <v>7.100576500081398</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04989262941632049</v>
+        <v>0.04932566771840777</v>
       </c>
       <c r="W89">
-        <v>0.2240353179836317</v>
+        <v>0.2241690075519995</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2625927864016868</v>
+        <v>0.259608777465304</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2464788269534893</v>
+        <v>0.2483788269534893</v>
       </c>
       <c r="C90">
-        <v>-1452.65373811705</v>
+        <v>-1481.657200740098</v>
       </c>
       <c r="D90">
-        <v>474.5102618829503</v>
+        <v>470.0597992599018</v>
       </c>
       <c r="E90">
-        <v>1257.364</v>
+        <v>1281.917</v>
       </c>
       <c r="F90">
-        <v>2160.664</v>
+        <v>2185.217</v>
       </c>
       <c r="G90">
         <v>233.5</v>
@@ -8792,37 +8792,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M90">
-        <v>509.4845712000001</v>
+        <v>515.2741686000001</v>
       </c>
       <c r="N90">
-        <v>-377.2179045333334</v>
+        <v>-383.0075019333334</v>
       </c>
       <c r="O90">
-        <v>-71.67140186133335</v>
+        <v>-72.77142536733335</v>
       </c>
       <c r="P90">
-        <v>-305.5465026720001</v>
+        <v>-310.2360765660001</v>
       </c>
       <c r="Q90">
-        <v>-251.5465026720001</v>
+        <v>-256.2360765660001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.410084169231081</v>
+        <v>0.4432009118884521</v>
       </c>
       <c r="T90">
-        <v>7.100576500081398</v>
+        <v>7.746083454634253</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04932566771840777</v>
+        <v>0.04877144673280768</v>
       </c>
       <c r="W90">
-        <v>0.2241690075519995</v>
+        <v>0.224299692860404</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.259608777465304</v>
+        <v>0.256691824909514</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2483788269534893</v>
+        <v>0.2502788269534892</v>
       </c>
       <c r="C91">
-        <v>-1481.657200740098</v>
+        <v>-1510.577956717088</v>
       </c>
       <c r="D91">
-        <v>470.0597992599018</v>
+        <v>465.6920432829123</v>
       </c>
       <c r="E91">
-        <v>1281.917</v>
+        <v>1306.47</v>
       </c>
       <c r="F91">
-        <v>2185.217</v>
+        <v>2209.77</v>
       </c>
       <c r="G91">
         <v>233.5</v>
@@ -8874,37 +8874,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M91">
-        <v>515.2741686000001</v>
+        <v>521.0637660000001</v>
       </c>
       <c r="N91">
-        <v>-383.0075019333334</v>
+        <v>-388.7970993333334</v>
       </c>
       <c r="O91">
-        <v>-72.77142536733335</v>
+        <v>-73.87144887333335</v>
       </c>
       <c r="P91">
-        <v>-310.2360765660001</v>
+        <v>-314.9256504600001</v>
       </c>
       <c r="Q91">
-        <v>-256.2360765660001</v>
+        <v>-260.9256504600001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4432009118884521</v>
+        <v>0.4829410030772973</v>
       </c>
       <c r="T91">
-        <v>7.746083454634253</v>
+        <v>8.520691800097678</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04877144673280768</v>
+        <v>0.0482295417691098</v>
       </c>
       <c r="W91">
-        <v>0.224299692860404</v>
+        <v>0.2244274740508439</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.256691824909514</v>
+        <v>0.2538396935216306</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2502788269534892</v>
+        <v>0.2521788269534893</v>
       </c>
       <c r="C92">
-        <v>-1510.577956717088</v>
+        <v>-1539.418290332163</v>
       </c>
       <c r="D92">
-        <v>465.6920432829123</v>
+        <v>461.4047096678368</v>
       </c>
       <c r="E92">
-        <v>1306.47</v>
+        <v>1331.023</v>
       </c>
       <c r="F92">
-        <v>2209.77</v>
+        <v>2234.323</v>
       </c>
       <c r="G92">
         <v>233.5</v>
@@ -8956,37 +8956,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M92">
-        <v>521.0637660000001</v>
+        <v>526.8533634000001</v>
       </c>
       <c r="N92">
-        <v>-388.7970993333334</v>
+        <v>-394.5866967333335</v>
       </c>
       <c r="O92">
-        <v>-73.87144887333335</v>
+        <v>-74.97147237933336</v>
       </c>
       <c r="P92">
-        <v>-314.9256504600001</v>
+        <v>-319.6152243540001</v>
       </c>
       <c r="Q92">
-        <v>-260.9256504600001</v>
+        <v>-265.6152243540001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4829410030772973</v>
+        <v>0.5315122256414415</v>
       </c>
       <c r="T92">
-        <v>8.520691800097678</v>
+        <v>9.467435333441866</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0482295417691098</v>
+        <v>0.04769954680461409</v>
       </c>
       <c r="W92">
-        <v>0.2244274740508439</v>
+        <v>0.224552446863472</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2538396935216306</v>
+        <v>0.2510502463400741</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2521788269534893</v>
+        <v>0.2540788269534893</v>
       </c>
       <c r="C93">
-        <v>-1539.418290332163</v>
+        <v>-1568.180402516978</v>
       </c>
       <c r="D93">
-        <v>461.4047096678368</v>
+        <v>457.195597483022</v>
       </c>
       <c r="E93">
-        <v>1331.023</v>
+        <v>1355.576</v>
       </c>
       <c r="F93">
-        <v>2234.323</v>
+        <v>2258.876</v>
       </c>
       <c r="G93">
         <v>233.5</v>
@@ -9038,37 +9038,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M93">
-        <v>526.8533634000001</v>
+        <v>532.6429608000001</v>
       </c>
       <c r="N93">
-        <v>-394.5866967333335</v>
+        <v>-400.3762941333334</v>
       </c>
       <c r="O93">
-        <v>-74.97147237933336</v>
+        <v>-76.07149588533335</v>
       </c>
       <c r="P93">
-        <v>-319.6152243540001</v>
+        <v>-324.3047982480001</v>
       </c>
       <c r="Q93">
-        <v>-265.6152243540001</v>
+        <v>-270.3047982480001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5315122256414415</v>
+        <v>0.5922262538466219</v>
       </c>
       <c r="T93">
-        <v>9.467435333441866</v>
+        <v>10.6508647501221</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04769954680461409</v>
+        <v>0.04718107346978134</v>
       </c>
       <c r="W93">
-        <v>0.224552446863472</v>
+        <v>0.2246747028758256</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2510502463400741</v>
+        <v>0.2483214393146386</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2540788269534893</v>
+        <v>0.2559788269534892</v>
       </c>
       <c r="C94">
-        <v>-1568.180402516978</v>
+        <v>-1596.866414618192</v>
       </c>
       <c r="D94">
-        <v>457.195597483022</v>
+        <v>453.0625853818079</v>
       </c>
       <c r="E94">
-        <v>1355.576</v>
+        <v>1380.129</v>
       </c>
       <c r="F94">
-        <v>2258.876</v>
+        <v>2283.429</v>
       </c>
       <c r="G94">
         <v>233.5</v>
@@ -9120,37 +9120,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M94">
-        <v>532.6429608000001</v>
+        <v>538.4325582</v>
       </c>
       <c r="N94">
-        <v>-400.3762941333334</v>
+        <v>-406.1658915333334</v>
       </c>
       <c r="O94">
-        <v>-76.07149588533335</v>
+        <v>-77.17151939133333</v>
       </c>
       <c r="P94">
-        <v>-324.3047982480001</v>
+        <v>-328.994372142</v>
       </c>
       <c r="Q94">
-        <v>-270.3047982480001</v>
+        <v>-274.994372142</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5922262538466219</v>
+        <v>0.6702871472532821</v>
       </c>
       <c r="T94">
-        <v>10.6508647501221</v>
+        <v>12.1724168572824</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04718107346978134</v>
+        <v>0.04667375009913853</v>
       </c>
       <c r="W94">
-        <v>0.2246747028758256</v>
+        <v>0.2247943297266231</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2483214393146386</v>
+        <v>0.2456513163112555</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2559788269534892</v>
+        <v>0.2578788269534893</v>
       </c>
       <c r="C95">
-        <v>-1596.866414618192</v>
+        <v>-1625.478371962455</v>
       </c>
       <c r="D95">
-        <v>453.0625853818079</v>
+        <v>449.0036280375453</v>
       </c>
       <c r="E95">
-        <v>1380.129</v>
+        <v>1404.682</v>
       </c>
       <c r="F95">
-        <v>2283.429</v>
+        <v>2307.982</v>
       </c>
       <c r="G95">
         <v>233.5</v>
@@ -9202,37 +9202,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M95">
-        <v>538.4325582</v>
+        <v>544.2221556000002</v>
       </c>
       <c r="N95">
-        <v>-406.1658915333334</v>
+        <v>-411.9554889333335</v>
       </c>
       <c r="O95">
-        <v>-77.17151939133333</v>
+        <v>-78.27154289733338</v>
       </c>
       <c r="P95">
-        <v>-328.994372142</v>
+        <v>-333.6839460360002</v>
       </c>
       <c r="Q95">
-        <v>-274.994372142</v>
+        <v>-279.6839460360002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6702871472532821</v>
+        <v>0.7743683384621626</v>
       </c>
       <c r="T95">
-        <v>12.1724168572824</v>
+        <v>14.20115300016281</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04667375009913853</v>
+        <v>0.0461772208427647</v>
       </c>
       <c r="W95">
-        <v>0.2247943297266231</v>
+        <v>0.2249114113252761</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2456513163112555</v>
+        <v>0.2430380044356037</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2578788269534893</v>
+        <v>0.2597788269534893</v>
       </c>
       <c r="C96">
-        <v>-1625.478371962455</v>
+        <v>-1654.018247231459</v>
       </c>
       <c r="D96">
-        <v>449.0036280375453</v>
+        <v>445.0167527685413</v>
       </c>
       <c r="E96">
-        <v>1404.682</v>
+        <v>1429.235</v>
       </c>
       <c r="F96">
-        <v>2307.982</v>
+        <v>2332.535</v>
       </c>
       <c r="G96">
         <v>233.5</v>
@@ -9284,37 +9284,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M96">
-        <v>544.2221556000002</v>
+        <v>550.0117530000001</v>
       </c>
       <c r="N96">
-        <v>-411.9554889333335</v>
+        <v>-417.7450863333335</v>
       </c>
       <c r="O96">
-        <v>-78.27154289733338</v>
+        <v>-79.37156640333336</v>
       </c>
       <c r="P96">
-        <v>-333.6839460360002</v>
+        <v>-338.3735199300001</v>
       </c>
       <c r="Q96">
-        <v>-279.6839460360002</v>
+        <v>-284.3735199300001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7743683384621626</v>
+        <v>0.9200820061545958</v>
       </c>
       <c r="T96">
-        <v>14.20115300016281</v>
+        <v>17.04138360019538</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0461772208427647</v>
+        <v>0.0456911448338935</v>
       </c>
       <c r="W96">
-        <v>0.2249114113252761</v>
+        <v>0.2250260280481679</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2430380044356037</v>
+        <v>0.2404797096520711</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2597788269534893</v>
+        <v>0.2616788269534893</v>
       </c>
       <c r="C97">
-        <v>-1654.018247231459</v>
+        <v>-1682.487943658767</v>
       </c>
       <c r="D97">
-        <v>445.0167527685413</v>
+        <v>441.1000563412331</v>
       </c>
       <c r="E97">
-        <v>1429.235</v>
+        <v>1453.788</v>
       </c>
       <c r="F97">
-        <v>2332.535</v>
+        <v>2357.088</v>
       </c>
       <c r="G97">
         <v>233.5</v>
@@ -9366,37 +9366,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M97">
-        <v>550.0117530000001</v>
+        <v>555.8013504</v>
       </c>
       <c r="N97">
-        <v>-417.7450863333335</v>
+        <v>-423.5346837333334</v>
       </c>
       <c r="O97">
-        <v>-79.37156640333336</v>
+        <v>-80.47158990933335</v>
       </c>
       <c r="P97">
-        <v>-338.3735199300001</v>
+        <v>-343.063093824</v>
       </c>
       <c r="Q97">
-        <v>-284.3735199300001</v>
+        <v>-289.063093824</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9200820061545958</v>
+        <v>1.138652507693245</v>
       </c>
       <c r="T97">
-        <v>17.04138360019538</v>
+        <v>21.30172950024423</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0456911448338935</v>
+        <v>0.04521519540854045</v>
       </c>
       <c r="W97">
-        <v>0.2250260280481679</v>
+        <v>0.2251382569226662</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2404797096520711</v>
+        <v>0.2379747126765287</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2616788269534893</v>
+        <v>0.2635788269534892</v>
       </c>
       <c r="C98">
-        <v>-1682.487943658767</v>
+        <v>-1710.889298059295</v>
       </c>
       <c r="D98">
-        <v>441.1000563412331</v>
+        <v>437.2517019407049</v>
       </c>
       <c r="E98">
-        <v>1453.788</v>
+        <v>1478.341</v>
       </c>
       <c r="F98">
-        <v>2357.088</v>
+        <v>2381.641</v>
       </c>
       <c r="G98">
         <v>233.5</v>
@@ -9448,37 +9448,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M98">
-        <v>555.8013504</v>
+        <v>561.5909478000001</v>
       </c>
       <c r="N98">
-        <v>-423.5346837333334</v>
+        <v>-429.3242811333334</v>
       </c>
       <c r="O98">
-        <v>-80.47158990933335</v>
+        <v>-81.57161341533336</v>
       </c>
       <c r="P98">
-        <v>-343.063093824</v>
+        <v>-347.7526677180001</v>
       </c>
       <c r="Q98">
-        <v>-289.063093824</v>
+        <v>-293.7526677180001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.138652507693242</v>
+        <v>1.502936676924323</v>
       </c>
       <c r="T98">
-        <v>21.30172950024417</v>
+        <v>28.40230600032557</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04521519540854045</v>
+        <v>0.04474905937340085</v>
       </c>
       <c r="W98">
-        <v>0.2251382569226662</v>
+        <v>0.2252481717997521</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2379747126765287</v>
+        <v>0.2355213651231624</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2635788269534892</v>
+        <v>0.2654788269534892</v>
       </c>
       <c r="C99">
-        <v>-1710.889298059295</v>
+        <v>-1739.224083701583</v>
       </c>
       <c r="D99">
-        <v>437.2517019407049</v>
+        <v>433.469916298417</v>
       </c>
       <c r="E99">
-        <v>1478.341</v>
+        <v>1502.894</v>
       </c>
       <c r="F99">
-        <v>2381.641</v>
+        <v>2406.194</v>
       </c>
       <c r="G99">
         <v>233.5</v>
@@ -9530,37 +9530,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M99">
-        <v>561.5909478000001</v>
+        <v>567.3805452</v>
       </c>
       <c r="N99">
-        <v>-429.3242811333334</v>
+        <v>-435.1138785333334</v>
       </c>
       <c r="O99">
-        <v>-81.57161341533336</v>
+        <v>-82.67163692133335</v>
       </c>
       <c r="P99">
-        <v>-347.7526677180001</v>
+        <v>-352.442241612</v>
       </c>
       <c r="Q99">
-        <v>-293.7526677180001</v>
+        <v>-298.442241612</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.502936676924323</v>
+        <v>2.231505015386484</v>
       </c>
       <c r="T99">
-        <v>28.40230600032557</v>
+        <v>42.60345900048835</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04474905937340085</v>
+        <v>0.04429243631857024</v>
       </c>
       <c r="W99">
-        <v>0.2252481717997521</v>
+        <v>0.2253558435160812</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2355213651231624</v>
+        <v>0.2331180858872117</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2654788269534892</v>
+        <v>0.2673788269534892</v>
       </c>
       <c r="C100">
-        <v>-1739.224083701583</v>
+        <v>-1767.49401303229</v>
       </c>
       <c r="D100">
-        <v>433.469916298417</v>
+        <v>429.7529869677105</v>
       </c>
       <c r="E100">
-        <v>1502.894</v>
+        <v>1527.447</v>
       </c>
       <c r="F100">
-        <v>2406.194</v>
+        <v>2430.747</v>
       </c>
       <c r="G100">
         <v>233.5</v>
@@ -9612,37 +9612,37 @@
         <v>132.2666666666667</v>
       </c>
       <c r="M100">
-        <v>567.3805452</v>
+        <v>573.1701426000001</v>
       </c>
       <c r="N100">
-        <v>-435.1138785333334</v>
+        <v>-440.9034759333334</v>
       </c>
       <c r="O100">
-        <v>-82.67163692133335</v>
+        <v>-83.77166042733336</v>
       </c>
       <c r="P100">
-        <v>-352.442241612</v>
+        <v>-357.1318155060001</v>
       </c>
       <c r="Q100">
-        <v>-298.442241612</v>
+        <v>-303.1318155060001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.231505015386484</v>
+        <v>4.417210030772968</v>
       </c>
       <c r="T100">
-        <v>42.60345900048835</v>
+        <v>85.2069180009767</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04429243631857024</v>
+        <v>0.04384503797191801</v>
       </c>
       <c r="W100">
-        <v>0.2253558435160812</v>
+        <v>0.2254613400462218</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2331180858872117</v>
+        <v>0.2307633577469369</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2673788269534892</v>
-      </c>
-      <c r="C101">
-        <v>-1767.49401303229</v>
-      </c>
-      <c r="D101">
-        <v>429.7529869677105</v>
-      </c>
-      <c r="E101">
-        <v>1527.447</v>
-      </c>
-      <c r="F101">
-        <v>2430.747</v>
-      </c>
-      <c r="G101">
-        <v>233.5</v>
-      </c>
-      <c r="H101">
-        <v>1552</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>186.2666666666667</v>
-      </c>
-      <c r="K101">
-        <v>54</v>
-      </c>
-      <c r="L101">
-        <v>132.2666666666667</v>
-      </c>
-      <c r="M101">
-        <v>573.1701426000001</v>
-      </c>
-      <c r="N101">
-        <v>-440.9034759333334</v>
-      </c>
-      <c r="O101">
-        <v>-83.77166042733336</v>
-      </c>
-      <c r="P101">
-        <v>-357.1318155060001</v>
-      </c>
-      <c r="Q101">
-        <v>-303.1318155060001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.417210030772968</v>
-      </c>
-      <c r="T101">
-        <v>85.2069180009767</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04384503797191801</v>
-      </c>
-      <c r="W101">
-        <v>0.2254613400462218</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2307633577469369</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
